--- a/docs/xlsx/jobs-2026-10-30.xlsx
+++ b/docs/xlsx/jobs-2026-10-30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="556">
   <si>
     <t>Title</t>
   </si>
@@ -38,13 +38,1657 @@
   </si>
   <si>
     <t>Link</t>
+  </si>
+  <si>
+    <t>2027 Crew Leader (April - November)</t>
+  </si>
+  <si>
+    <t>Wisconsin Conservation Corps</t>
+  </si>
+  <si>
+    <t>La Crosse, WI</t>
+  </si>
+  <si>
+    <t>AmeriCorps</t>
+  </si>
+  <si>
+    <t>$550 per week</t>
+  </si>
+  <si>
+    <t>general-stewardship-outdoor-recreation-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-2027-crew-leader-april---november-la-crosse-wisconsin/1481867669</t>
+  </si>
+  <si>
+    <t>Biologist</t>
+  </si>
+  <si>
+    <t>Ducks Unlimited</t>
+  </si>
+  <si>
+    <t>Fergus Falls, MN</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>$55,000 - $70,000 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-biologist-fergus-falls-minnesota/7069615239</t>
+  </si>
+  <si>
+    <t>Brown Treesnake (BTS) Control and Native Species Recovery Crew Lead-5 - Guam</t>
+  </si>
+  <si>
+    <t>CEMML</t>
+  </si>
+  <si>
+    <t>Santa Rita, Guam, Other</t>
+  </si>
+  <si>
+    <t>$50,000 - $57,000 per year</t>
+  </si>
+  <si>
+    <t>restoration-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-brown-treesnake-bts-control-and-native-species-recovery-crew-lead-5---guam-santa-rita-guam-other/3726629584</t>
+  </si>
+  <si>
+    <t>Conservation Manager</t>
+  </si>
+  <si>
+    <t>Mississippi Valley Conservancy</t>
+  </si>
+  <si>
+    <t>$65,000 - $75,000 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-conservation-manager-la-crosse-wisconsin/1041079716</t>
+  </si>
+  <si>
+    <t>Deputy Director of Organizing and Campaigns</t>
+  </si>
+  <si>
+    <t>Northern Plains</t>
+  </si>
+  <si>
+    <t>Billings, MT</t>
+  </si>
+  <si>
+    <t>$65,000 - $70,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-deputy-director-of-organizing-and-campaigns-billings-montana/2091484415</t>
+  </si>
+  <si>
+    <t>District Support Specialist</t>
+  </si>
+  <si>
+    <t>Indiana State Department of Agriculture</t>
+  </si>
+  <si>
+    <t>Fort Wayne, IN</t>
+  </si>
+  <si>
+    <t>$53,222 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship-hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-district-support-specialist-fort-wayne-indiana/8871080749</t>
+  </si>
+  <si>
+    <t>Ecozone Gardener</t>
+  </si>
+  <si>
+    <t>Prospect Park Alliance</t>
+  </si>
+  <si>
+    <t>Brooklyn, NY</t>
+  </si>
+  <si>
+    <t>$24 per hour</t>
+  </si>
+  <si>
+    <t>general-stewardship-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-ecozone-gardener-brooklyn-new-york/4786079310</t>
+  </si>
+  <si>
+    <t>Environmental Policy &amp; Advocacy Associate</t>
+  </si>
+  <si>
+    <t>Sanibel-Captiva Conservation Foundation</t>
+  </si>
+  <si>
+    <t>Sanibel, FL</t>
+  </si>
+  <si>
+    <t>$55,000 - $60,000 per year</t>
+  </si>
+  <si>
+    <t>policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-policy--advocacy-associate-sanibel-florida/5063722059</t>
+  </si>
+  <si>
+    <t>Equipment Operator, Forest Nursery Technician</t>
+  </si>
+  <si>
+    <t>Washington State Department of Natural Resources</t>
+  </si>
+  <si>
+    <t>Olympia, WA</t>
+  </si>
+  <si>
+    <t>$3,738 - $4,980 per month</t>
+  </si>
+  <si>
+    <t>forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-equipment-operator-forest-nursery-technician-olympia-washington/8448850838</t>
+  </si>
+  <si>
+    <t>Florida Grasshopper Sparrow Internship</t>
+  </si>
+  <si>
+    <t>White Oak Conservation</t>
+  </si>
+  <si>
+    <t>Yulee, FL</t>
+  </si>
+  <si>
+    <t>Paid Internship</t>
+  </si>
+  <si>
+    <t>$2,400 per month</t>
+  </si>
+  <si>
+    <t>wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-florida-grasshopper-sparrow-internship-yulee-florida/7446805281</t>
+  </si>
+  <si>
+    <t>Forest Nursery Laborer</t>
+  </si>
+  <si>
+    <t>Temporary</t>
+  </si>
+  <si>
+    <t>$3,195 - $4,201 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-forest-nursery-laborer-olympia-washington/2681533552</t>
+  </si>
+  <si>
+    <t>Forestry Nursery Lead</t>
+  </si>
+  <si>
+    <t>$3,327 - $4,406 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-forestry-nursery-lead-olympia-washington/4289600873</t>
+  </si>
+  <si>
+    <t>Game and Fish Technician - Fort Polk, LA</t>
+  </si>
+  <si>
+    <t>Fort Polk, LA</t>
+  </si>
+  <si>
+    <t>$45,000 - $52,000 per year</t>
+  </si>
+  <si>
+    <t>fisheries-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-game-and-fish-technician---fort-polk-la-fort-polk-louisiana/7848147516</t>
+  </si>
+  <si>
+    <t>Natural Resource GIS Applications Supervisor</t>
+  </si>
+  <si>
+    <t>Ellensburg, WA</t>
+  </si>
+  <si>
+    <t>$90,084 - $121,176 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-natural-resource-gis-applications-supervisor-ellensburg-washington/7942544295</t>
+  </si>
+  <si>
+    <t>Operations Coordinator</t>
+  </si>
+  <si>
+    <t>Friends of the Gorge</t>
+  </si>
+  <si>
+    <t>Portland, OR</t>
+  </si>
+  <si>
+    <t>$52,000 - $57,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-operations-coordinator-portland-oregon/3226531841</t>
+  </si>
+  <si>
+    <t>Partnership Projects Manager</t>
+  </si>
+  <si>
+    <t>Grand Teton National Park Foundation</t>
+  </si>
+  <si>
+    <t>Jackson, WY</t>
+  </si>
+  <si>
+    <t>$70,000 - $85,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-partnership-projects-manager-jackson-wyoming/3935657610</t>
+  </si>
+  <si>
+    <t>Philanthropy Officer</t>
+  </si>
+  <si>
+    <t>$85,000 - $95,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-philanthropy-officer-portland-oregon/1254846213</t>
+  </si>
+  <si>
+    <t>Restoration, Invasive Species, and Forestry Technician</t>
+  </si>
+  <si>
+    <t>Redstart</t>
+  </si>
+  <si>
+    <t>Corinth, VT</t>
+  </si>
+  <si>
+    <t>$16-18/hour DOE</t>
+  </si>
+  <si>
+    <t>botany-forestry-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-restoration-invasive-species-and-forestry-technician-corinth-vermont/1713322448</t>
+  </si>
+  <si>
+    <t>School Year Program Instructor (2027)</t>
+  </si>
+  <si>
+    <t>Vida Verde Nature Education</t>
+  </si>
+  <si>
+    <t>San Gregorio, CA</t>
+  </si>
+  <si>
+    <t>$18 - $20 per hour</t>
+  </si>
+  <si>
+    <t>environmental-education</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-school-year-program-instructor-2027-san-gregorio-california/6256566444</t>
+  </si>
+  <si>
+    <t>Technical Advisor - Law Enforcement and Wildlife Crime Prevention.</t>
+  </si>
+  <si>
+    <t>Wild Conservation Society</t>
+  </si>
+  <si>
+    <t>Libreville, Africa</t>
+  </si>
+  <si>
+    <t>Competitive Salary commensurate with Experience</t>
+  </si>
+  <si>
+    <t>marine-biology-policy-and-law-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-technical-advisor---law-enforcement-and-wildlife-crime-prevention-libreville-africa/7241973978</t>
+  </si>
+  <si>
+    <t>USFS Forest Archeology Strike Team Crew Leader I</t>
+  </si>
+  <si>
+    <t>Conservation Corps North Carolina</t>
+  </si>
+  <si>
+    <t>Uwharrie National Forest, NC</t>
+  </si>
+  <si>
+    <t>$20 - $25 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-usfs-forest-archeology-strike-team-crew-leader-i-uwharrie-national-forest-north-carolina/1397827741</t>
+  </si>
+  <si>
+    <t>Visitor Outreach Technician (NPS, Joshua Tree National Park)</t>
+  </si>
+  <si>
+    <t>Great Basin Institute</t>
+  </si>
+  <si>
+    <t>Twentynine Palms, CA</t>
+  </si>
+  <si>
+    <t>$24.00/hr</t>
+  </si>
+  <si>
+    <t>environmental-education-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-visitor-outreach-technician-nps-joshua-tree-national-park-twentynine-palms-california/3424867469</t>
+  </si>
+  <si>
+    <t>Water Quality Research Intern</t>
+  </si>
+  <si>
+    <t>Phinizy Center for Water Sciences</t>
+  </si>
+  <si>
+    <t>Augusta, GA</t>
+  </si>
+  <si>
+    <t>Unpaid</t>
+  </si>
+  <si>
+    <t>Unpaid position</t>
+  </si>
+  <si>
+    <t>ecology-hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-water-quality-research-intern-augusta-georgia/2000346421</t>
+  </si>
+  <si>
+    <t>Water Resources Manager</t>
+  </si>
+  <si>
+    <t>Arizona Game and Fish Department</t>
+  </si>
+  <si>
+    <t>Phoenix, AZ</t>
+  </si>
+  <si>
+    <t>$60,000 - $75,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-water-resources-manager-phoenix-arizona/6627122359</t>
+  </si>
+  <si>
+    <t>Wilderness Outfitting Assistant</t>
+  </si>
+  <si>
+    <t>Ely Outfitting Company</t>
+  </si>
+  <si>
+    <t>Ely, MN</t>
+  </si>
+  <si>
+    <t>Competitive pay + end of summer bonus</t>
+  </si>
+  <si>
+    <t>outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wilderness-outfitting-assistant-ely-minnesota/9972490056</t>
+  </si>
+  <si>
+    <t>(1) Educational AmeriCorps Position working with Immigrant Youth</t>
+  </si>
+  <si>
+    <t>Oakland International High School</t>
+  </si>
+  <si>
+    <t>Oakland, California</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 2314.00 - 2314.00/month</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/e238641dcbdc4e54b59cb001d0726473-1-educational-americorps-position-working-with-immigrant-youth-oakland-international-high-school-oakland</t>
+  </si>
+  <si>
+    <t>Administrative Assistant, Executive Office Team</t>
+  </si>
+  <si>
+    <t>Blue Meridian Partners</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 88000.00 - 88000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9e3b434bf4644b5693831220d88a2cd5-administrative-assistant-executive-office-team-blue-meridian-partners-new-york</t>
+  </si>
+  <si>
+    <t>Assistant Attorney General</t>
+  </si>
+  <si>
+    <t>Office of the Massachusetts Attorney General</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 90125.00 - 134513.00/year</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/535caee89cd0475aa2308b4c9692316a-assistant-attorney-general-office-of-the-massachusetts-attorney-general-boston</t>
+  </si>
+  <si>
+    <t>Assistant General Counsel</t>
+  </si>
+  <si>
+    <t>Hadassah, WZOA, Inc.</t>
+  </si>
+  <si>
+    <t>USD 146067.00 - 165000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Health Medicine, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/602780447b164b5fbf43a42186d4641a-assistant-general-counsel-hadassah-wzoa-inc-new-york</t>
+  </si>
+  <si>
+    <t>Bilingual Content Creator</t>
+  </si>
+  <si>
+    <t>Siembra NC</t>
+  </si>
+  <si>
+    <t>Raleigh, North Carolina</t>
+  </si>
+  <si>
+    <t>USD 71500.00 - 76500.00/year</t>
+  </si>
+  <si>
+    <t>Policy, Human Rights Civil Liberties, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b01db8baedab4fcc963f2841578b8f9a-bilingual-content-creator-siembra-nc-raleigh</t>
+  </si>
+  <si>
+    <t>Case Manager</t>
+  </si>
+  <si>
+    <t>Beautiful Day Granola</t>
+  </si>
+  <si>
+    <t>Providence, Rhode Island</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 52000.00/year</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees, Human Rights Civil Liberties, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b74b8474113545b2bc533b305e51b5bc-case-manager-beautiful-day-granola-providence</t>
+  </si>
+  <si>
+    <t>Chief Executive Officer (CEO)</t>
+  </si>
+  <si>
+    <t>N Street Village</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 220000.00 - 240000.00/year</t>
+  </si>
+  <si>
+    <t>Women, Housing Homelessness, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/9068b2c56f57488c8369e00da93e5b10-chief-executive-officer-ceo-n-street-village-washington</t>
+  </si>
+  <si>
+    <t>Communications and Development Associate</t>
+  </si>
+  <si>
+    <t>The Future of Heat Institute</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Energy, Environment, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fc8248a126754bb690306a37f4522a1a-communications-and-development-associate-the-future-of-heat-institute-new-york</t>
+  </si>
+  <si>
+    <t>Communications Manager or Director</t>
+  </si>
+  <si>
+    <t>Farm and Ranch Freedom Alliance</t>
+  </si>
+  <si>
+    <t>Remote (Texas)</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d5ddb5926dc04c8faebfdd546f00d81e-communications-manager-or-director-farm-and-ranch-freedom-alliance-cameron</t>
+  </si>
+  <si>
+    <t>Community Manager</t>
+  </si>
+  <si>
+    <t>The Pearl Works</t>
+  </si>
+  <si>
+    <t>Monterey, California</t>
+  </si>
+  <si>
+    <t>USD 24.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Entrepreneurship, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/fea0d6d35fe44dfb9565361ccff99486-community-manager-the-pearl-works-monterey</t>
+  </si>
+  <si>
+    <t>Community Organizer (Youth, Housing Justice &amp; Resident Leadership)</t>
+  </si>
+  <si>
+    <t>NeighborWorks Affiliates</t>
+  </si>
+  <si>
+    <t>USD 60000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1b4e6ff9b9ef453fb21637dc2c33d3fa-community-organizer-youth-housing-justice-resident-leadership-neighborworks-affiliates-boston</t>
+  </si>
+  <si>
+    <t>Community Recruiter</t>
+  </si>
+  <si>
+    <t>Small Magic</t>
+  </si>
+  <si>
+    <t>Birmingham, Alabama</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e7081c21d5ba42bbaafc4bcaef2e31d3-community-recruiter-small-magic-birmingham</t>
+  </si>
+  <si>
+    <t>Coordinator, Programs and Events</t>
+  </si>
+  <si>
+    <t>New York Genealogical &amp; Biographical Society</t>
+  </si>
+  <si>
+    <t>USD 62000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Science Technology, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3874267206fc4582ae5286d09e62bb58-coordinator-programs-and-events-new-york-genealogical-biographical-society-new-york</t>
+  </si>
+  <si>
+    <t>Development Associate - Temporary</t>
+  </si>
+  <si>
+    <t>SELT (Southeast Land Trust of New Hampshire)</t>
+  </si>
+  <si>
+    <t>Epping, New Hampshire</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 22.00 - 24.00/hour</t>
+  </si>
+  <si>
+    <t>Climate Change, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cf3dbf1fca124c15ac476a15a02778b4-development-associate-temporary-selt-southeast-land-trust-of-new-hampshire-epping</t>
+  </si>
+  <si>
+    <t>Digital Communications Strategist</t>
+  </si>
+  <si>
+    <t>ACLU of the District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 104999.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1cd50d0c99a448da988c50e37c4834cf-digital-communications-strategist-aclu-of-the-district-of-columbia-washington</t>
+  </si>
+  <si>
+    <t>Digital Fundraiser</t>
+  </si>
+  <si>
+    <t>Amazon Watch</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2266308def6241999f1111c15e4089c6-digital-fundraiser-amazon-watch-oakland</t>
+  </si>
+  <si>
+    <t>Director of Clinical Services</t>
+  </si>
+  <si>
+    <t>Sarah's Circle (Chicago)</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>USD 86000.00 - 108000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Lgbtq, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1314c00650f44aa2956cbf5f8ca2ab11-director-of-clinical-services-sarahs-circle-chicago-chicago</t>
+  </si>
+  <si>
+    <t>Director of Content &amp; Governance Education</t>
+  </si>
+  <si>
+    <t>BoardSource</t>
+  </si>
+  <si>
+    <t>USD 128000.00 - 160000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/9553911c6d884f0a81258da639a62c34-director-of-content-governance-education-boardsource-washington</t>
+  </si>
+  <si>
+    <t>Director of Development</t>
+  </si>
+  <si>
+    <t>Casey Trees</t>
+  </si>
+  <si>
+    <t>USD 145000.00 - 155000.00/year</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f5f5717e17924341a10d9cf5ba799384-director-of-development-casey-trees-washington</t>
+  </si>
+  <si>
+    <t>Director of Development and Communications</t>
+  </si>
+  <si>
+    <t>Mainspring Schools</t>
+  </si>
+  <si>
+    <t>Austin, Texas</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b1f39caa4ce8445da92316b2aca0fa8c-director-of-development-and-communications-mainspring-schools-austin</t>
+  </si>
+  <si>
+    <t>Director of Finance</t>
+  </si>
+  <si>
+    <t>Protect Democracy</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>USD 166600.00 - 186000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d6e2dceae2954b7b89f4fbef8673d45e-director-of-finance-protect-democracy-washington</t>
+  </si>
+  <si>
+    <t>Director of Operations, OAC</t>
+  </si>
+  <si>
+    <t>Jewish Community Council of Greater Coney Island</t>
+  </si>
+  <si>
+    <t>Kings County, New York</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/82f03b3604ea493097a247fd42b7594a-director-of-operations-oac-jewish-community-council-of-greater-coney-island-kings-county</t>
+  </si>
+  <si>
+    <t>Director, Philanthropic Operations</t>
+  </si>
+  <si>
+    <t>Trust for the National Mall</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Environment, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/894442fb8f994ccd816b7ce535dd6ff4-director-philanthropic-operations-trust-for-the-national-mall-washington</t>
+  </si>
+  <si>
+    <t>Donor Operations Coordinator</t>
+  </si>
+  <si>
+    <t>The Choice Inc</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Disaster Relief, Climate Change, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/5a437eb42383476d8d4ef223a09180eb-donor-operations-coordinator-the-choice-inc-washington</t>
+  </si>
+  <si>
+    <t>Executive Administrative Assistant</t>
+  </si>
+  <si>
+    <t>Chicago South Side Birth Center</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Reproductive Health Rights</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/328b8cbbcfa14b3d960c4f525e8c5597-executive-administrative-assistant-chicago-south-side-birth-center-chicago</t>
+  </si>
+  <si>
+    <t>Executive Assistant to the Executive Director</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 67000.00 - 77500.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d848dc37f85b4cac80079a55856a140a-executive-assistant-to-the-executive-director-small-magic-birmingham</t>
+  </si>
+  <si>
+    <t>Executive Director</t>
+  </si>
+  <si>
+    <t>Rescue Cats Rock Inc DBA The Cat Ranch</t>
+  </si>
+  <si>
+    <t>Babcock Ranch, FL</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Animals</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4de54369879e4c309045bd5f9601d3bd-executive-director-rescue-cats-rock-inc-dba-the-cat-ranch-babcock-ranch</t>
+  </si>
+  <si>
+    <t>Appendix Cancer PMP Research Foundation</t>
+  </si>
+  <si>
+    <t>Education, Health Medicine, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7d9c569810ae47ecb6dbd938d4191619-executive-director-appendix-cancer-pmp-research-foundation-springfield</t>
+  </si>
+  <si>
+    <t>Executive Director / CEO</t>
+  </si>
+  <si>
+    <t>Reach Out and Read Colorado</t>
+  </si>
+  <si>
+    <t>Denver, Colorado</t>
+  </si>
+  <si>
+    <t>USD 125000.00 - 145000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5d121dd4189142e9bcd1bdbbefa2c6ef-executive-director-ceo-reach-out-and-read-colorado-denver</t>
+  </si>
+  <si>
+    <t>Family Engagement Specialist</t>
+  </si>
+  <si>
+    <t>USD 54000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/70b640971052400e840ea17781a2f811-family-engagement-specialist-small-magic-birmingham</t>
+  </si>
+  <si>
+    <t>Family Law Attorney</t>
+  </si>
+  <si>
+    <t>South Asian Network (SAN)</t>
+  </si>
+  <si>
+    <t>Artesia, CA</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>Women, Victim Support, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5803b25e16b34831a9440fddcfe65b68-family-law-attorney-south-asian-network-san-artesia</t>
+  </si>
+  <si>
+    <t>Grants Administrator (Research Programs Specialist) - Office of Research &amp; Sponsored Programs</t>
+  </si>
+  <si>
+    <t>The Graduate Center, CUNY</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/596a64abb9584ca2bbb485852ab133e5-grants-administrator-research-programs-specialist-office-of-research-sponsored-programs-the-graduate-center-cuny-new-york</t>
+  </si>
+  <si>
+    <t>HR Manager</t>
+  </si>
+  <si>
+    <t>Pivot (Madagascar)</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Research Social Science, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5bf7e440780b42ddbbbdb0532e4edd84-hr-manager-pivot-madagascar-boston</t>
+  </si>
+  <si>
+    <t>Information Tech Specialist</t>
+  </si>
+  <si>
+    <t>Louis D. Brown Peace Institute</t>
+  </si>
+  <si>
+    <t>USD 30.77 - 34.62/hour</t>
+  </si>
+  <si>
+    <t>Family, Urban Areas, Victim Support</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b52afbb4d0734d39862a800713710de6-information-tech-specialist-louis-d-brown-peace-institute-boston</t>
+  </si>
+  <si>
+    <t>Investigator 3, Law &amp; Public Safety (Drug Affordability Compliance Officer)</t>
+  </si>
+  <si>
+    <t>New Jersey Attorney General's Office</t>
+  </si>
+  <si>
+    <t>Newark, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 72896.47 - 106798.07/year</t>
+  </si>
+  <si>
+    <t>Job Workplace, Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/f5fa2b19e3b64c80b320d3aee7bfcad0-investigator-3-law-public-safety-drug-affordability-compliance-officer-new-jersey-attorney-generals-office-newark</t>
+  </si>
+  <si>
+    <t>Jr. Research Scientist / Program Assistant, Protection Services</t>
+  </si>
+  <si>
+    <t>Scholars at Risk</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 57000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Human Rights Civil Liberties, International Relations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/eccbb3ddc3ef40529b0a9fee1844c4e8-jr-research-scientist-program-assistant-protection-services-scholars-at-risk-new-york</t>
+  </si>
+  <si>
+    <t>League Associate, Teacher (San Francisco, Menlo, Woodside, Hillsborough)</t>
+  </si>
+  <si>
+    <t>League of Creative Minds, Academy of Debate and Diplomacy</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 80000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Children Youth, Conflict Resolution</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/ec2bdbe563954af2a2aac34265706f33-league-associate-teacher-san-francisco-menlo-woodside-hillsborough-league-of-creative-minds-academy-of-debate-and-diplomacy-san-francisco</t>
+  </si>
+  <si>
+    <t>Legal Assistant</t>
+  </si>
+  <si>
+    <t>California Center for Movement Legal Services</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>USD 54000.00 - 58000.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e3e14db7d9e6467ba84e929c016f909e-legal-assistant-california-center-for-movement-legal-services-los-angeles</t>
+  </si>
+  <si>
+    <t>Major Gift Officer - West Coast</t>
+  </si>
+  <si>
+    <t>National Outdoor Leadership School (NOLS)</t>
+  </si>
+  <si>
+    <t>Remote (California)</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2a7e980b9ffb4e68ae1f7af3b42a4357-major-gift-officer-west-coast-national-outdoor-leadership-school-nols-lander</t>
+  </si>
+  <si>
+    <t>Manager, Donor Engagement</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 77000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fa10f90d74d94ed6950e77a79f5811af-manager-donor-engagement-trust-for-the-national-mall-washington</t>
+  </si>
+  <si>
+    <t>Manager, Philanthropy Reporting and Projects</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Women, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6d5dfa8587da408bad6ce4d221ce3bd5-manager-philanthropy-reporting-and-projects-hadassah-wzoa-inc-new-york</t>
+  </si>
+  <si>
+    <t>Market Program Coordinator, Fairhill (Bilingual English/Spanish)</t>
+  </si>
+  <si>
+    <t>Small Things, Inc.</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e9fd3874e8a44082a9146948c2e51860-market-program-coordinator-fairhill-bilingual-englishspanish-small-things-inc-philadelphia</t>
+  </si>
+  <si>
+    <t>Marketing &amp; Communications Assistant</t>
+  </si>
+  <si>
+    <t>Princeton Public Library</t>
+  </si>
+  <si>
+    <t>Princeton, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/bf974d9ca47f47e3824c3d93d5d0a54a-marketing-communications-assistant-princeton-public-library-princeton</t>
+  </si>
+  <si>
+    <t>Marketing Manager, Lead Generation</t>
+  </si>
+  <si>
+    <t>National Equity Project</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2599785102504d5eb13cb1daddef5e24-marketing-manager-lead-generation-national-equity-project-oakland</t>
+  </si>
+  <si>
+    <t>Movement Manager - Remote California</t>
+  </si>
+  <si>
+    <t>Compassion and Choices</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/697a5dcb850e4c229ede1e2a61a4cecf-movement-manager-remote-california-compassion-and-choices-porterville</t>
+  </si>
+  <si>
+    <t>Movement Manager - Remote Florida</t>
+  </si>
+  <si>
+    <t>Remote (Florida)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/893655ec7680485ea26e3b5e9dbdd648-movement-manager-remote-florida-compassion-and-choices-lake-city</t>
+  </si>
+  <si>
+    <t>Movement Manager - Remote New York</t>
+  </si>
+  <si>
+    <t>Remote (New York)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b98d5a812aa244afa91b342bbd886977-movement-manager-remote-new-york-compassion-and-choices-albany</t>
+  </si>
+  <si>
+    <t>Non-profit Governance Coordinator</t>
+  </si>
+  <si>
+    <t>American Society of Clinical Oncology</t>
+  </si>
+  <si>
+    <t>Alexandria, VA</t>
+  </si>
+  <si>
+    <t>Education, Health Medicine, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/91bea95acab14aefa6df66bd6f073210-non-profit-governance-coordinator-american-society-of-clinical-oncology-alexandria</t>
+  </si>
+  <si>
+    <t>Operations and Human Resources Assistant</t>
+  </si>
+  <si>
+    <t>United States of Care</t>
+  </si>
+  <si>
+    <t>Remote (District of Columbia)</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Health Medicine, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e61e9cde2abc46bab9ffc5ec76c58cbd-operations-and-human-resources-assistant-united-states-of-care-washington</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 50000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3249d3d67ed249d9baed61a359968dab-operations-coordinator-small-magic-birmingham</t>
+  </si>
+  <si>
+    <t>Outreach Coordinator</t>
+  </si>
+  <si>
+    <t>Bricks and Mortals</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Housing Homelessness, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fd0ceab2b174419d84cd81d5bddb7b89-outreach-coordinator-bricks-and-mortals-new-york</t>
+  </si>
+  <si>
+    <t>Part-Time After School Elementary Math Educator</t>
+  </si>
+  <si>
+    <t>The Art of Problem Solving Initiative, Inc.</t>
+  </si>
+  <si>
+    <t>USD 40.00 - 40.00/hour</t>
+  </si>
+  <si>
+    <t>Education, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/79a7bb62acc14889a4e378053c6468e4-part-time-after-school-elementary-math-educator-the-art-of-problem-solving-initiative-inc-new-york</t>
+  </si>
+  <si>
+    <t>Part-time Associate</t>
+  </si>
+  <si>
+    <t>Benvenuti Arts</t>
+  </si>
+  <si>
+    <t>Arts Music</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/f3a7132d8c66490f97f9840e79dd7186-part-time-associate-benvenuti-arts-pittsburgh</t>
+  </si>
+  <si>
+    <t>Partnerships &amp; Recruitment Manager (Part-Time)</t>
+  </si>
+  <si>
+    <t>New Majority Capital Foundation</t>
+  </si>
+  <si>
+    <t>Remote (Illinois)</t>
+  </si>
+  <si>
+    <t>USD 40.00 - 45.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8449b1763aa74fb7998fecf0899f1957-partnerships-recruitment-manager-part-time-new-majority-capital-foundation-boston</t>
+  </si>
+  <si>
+    <t>Philanthropic Advisor</t>
+  </si>
+  <si>
+    <t>Combined Jewish Philanthropies</t>
+  </si>
+  <si>
+    <t>USD 126200.00 - 157800.00/year</t>
+  </si>
+  <si>
+    <t>Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/473fe19a3631463a8b532ee5146d845e-philanthropic-advisor-combined-jewish-philanthropies-boston</t>
+  </si>
+  <si>
+    <t>Principal Giving Officer</t>
+  </si>
+  <si>
+    <t>USD 141100.00 - 166000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9dd7a557070c4042ae6e113cc118859c-principal-giving-officer-protect-democracy-washington</t>
+  </si>
+  <si>
+    <t>Program Assistant – Training Department</t>
+  </si>
+  <si>
+    <t>CPWR-The Center for Construction Research and Training</t>
+  </si>
+  <si>
+    <t>Silver Spring, Maryland</t>
+  </si>
+  <si>
+    <t>USD 41000.00 - 44000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6193796dc304479ba514be870b6a62b6-program-assistant-training-department-cpwr-the-center-for-construction-research-and-training-silver-spring</t>
+  </si>
+  <si>
+    <t>Program Assistant, Energy Employees Unit</t>
+  </si>
+  <si>
+    <t>Health Medicine, Job Workplace, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/87c0b00de18342dcaf756ded6423231c-program-assistant-energy-employees-unit-cpwr-the-center-for-construction-research-and-training-silver-spring</t>
+  </si>
+  <si>
+    <t>Program Coordinator, Learning, Culture &amp; Community</t>
+  </si>
+  <si>
+    <t>DOROT</t>
+  </si>
+  <si>
+    <t>USD 58000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Seniors Retirement, Volunteering, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/314f0f43470d4297907727dc243d5c16-program-coordinator-learning-culture-community-dorot-new-york</t>
+  </si>
+  <si>
+    <t>Program Director</t>
+  </si>
+  <si>
+    <t>Staten Island Arts</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9a4b641af92a4df587f84c81dfd3a53b-program-director-staten-island-arts-new-york</t>
+  </si>
+  <si>
+    <t>Program Director, Childcare Centers</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9050c32014ea41bb8fef2a4b9e51233e-program-director-childcare-centers-small-magic-birmingham</t>
+  </si>
+  <si>
+    <t>Program Manager—Middle &amp; High School Youth Development</t>
+  </si>
+  <si>
+    <t>Seeds 4 Success</t>
+  </si>
+  <si>
+    <t>Annapolis, Maryland</t>
+  </si>
+  <si>
+    <t>USD 48000.00 - 52000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f4217d71897d46feb137298aa5535a03-program-managermiddle-high-school-youth-development-seeds-4-success-annapolis</t>
+  </si>
+  <si>
+    <t>Program Support Coordinator (part-time)</t>
+  </si>
+  <si>
+    <t>Playtime Project</t>
+  </si>
+  <si>
+    <t>USD 25.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9d7d3041454846798ef68c423c576613-program-support-coordinator-part-time-playtime-project-washington</t>
+  </si>
+  <si>
+    <t>Project Manager Digital Transformation</t>
+  </si>
+  <si>
+    <t>Welthungerhilfe</t>
+  </si>
+  <si>
+    <t>Bonn, Nordrhein-Westfalen, DE</t>
+  </si>
+  <si>
+    <t>Agriculture, Disaster Relief, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/013c33863a6d4be59afbaa408ed47d4d-project-manager-digital-transformation-welthungerhilfe-bonn</t>
+  </si>
+  <si>
+    <t>Public Defender Client Advocate in Lancaster, California</t>
+  </si>
+  <si>
+    <t>Partners for Justice</t>
+  </si>
+  <si>
+    <t>Lancaster, California</t>
+  </si>
+  <si>
+    <t>USD 52400.00 - 55980.00/year</t>
+  </si>
+  <si>
+    <t>Crime Safety, Human Rights Civil Liberties, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/62173c13db95490ba5f4eca6716062c3-public-defender-client-advocate-in-lancaster-california-partners-for-justice-lancaster</t>
+  </si>
+  <si>
+    <t>Public Defender Client Advocate in San Fernando, CA</t>
+  </si>
+  <si>
+    <t>San Fernando, California</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/807e18d0768f4459abb81e7def6c4d58-public-defender-client-advocate-in-san-fernando-ca-partners-for-justice-san-fernando</t>
+  </si>
+  <si>
+    <t>Regional Associate, Northwest</t>
+  </si>
+  <si>
+    <t>J Street</t>
+  </si>
+  <si>
+    <t>USD 62000.00 - 67000.00/year</t>
+  </si>
+  <si>
+    <t>Conflict Resolution, Education, International Relations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ffbf888a62e348539631f1cbacaca088-regional-associate-northwest-j-street-san-francisco</t>
+  </si>
+  <si>
+    <t>Regional Coordinator, Summer Work and Travel (MA)</t>
+  </si>
+  <si>
+    <t>CIEE: Council on International Educational Exchange</t>
+  </si>
+  <si>
+    <t>Remote (Massachusetts)</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education, International Relations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bf469a279163403881ad8316a3ba07a6-regional-coordinator-summer-work-and-travel-ma-ciee-council-on-international-educational-exchange-portland</t>
+  </si>
+  <si>
+    <t>Regional Coordinator, Summer Work and Travel (MT)</t>
+  </si>
+  <si>
+    <t>Remote (Montana)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/05abed1dc8e440e4b5f323225f97c696-regional-coordinator-summer-work-and-travel-mt-ciee-council-on-international-educational-exchange-portland</t>
+  </si>
+  <si>
+    <t>Relationship Manager, DC, Maryland and Virginia</t>
+  </si>
+  <si>
+    <t>USD 59500.00 - 72000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5d58e1fc685b463e8616dc1f3df4d021-relationship-manager-dc-maryland-and-virginia-j-street-washington</t>
+  </si>
+  <si>
+    <t>Salesforce Administrator and Business Analyst</t>
+  </si>
+  <si>
+    <t>Wilshire Boulevard Temple</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/30611350e206447f8186a5a70f42e988-salesforce-administrator-and-business-analyst-wilshire-boulevard-temple-los-angeles</t>
+  </si>
+  <si>
+    <t>Senior Advisor, Affiliate Legal Programs</t>
+  </si>
+  <si>
+    <t>American Civil Liberties Union</t>
+  </si>
+  <si>
+    <t>USD 167568.00 - 167568.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Policy, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1e69da5b0cb24ad1ac4e764343d6d1ad-senior-advisor-affiliate-legal-programs-american-civil-liberties-union-new-york</t>
+  </si>
+  <si>
+    <t>Senior Employment Law Attorney</t>
+  </si>
+  <si>
+    <t>Open Door Legal</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4ca9f6083b3f426090c965fbe518c154-senior-employment-law-attorney-open-door-legal-san-francisco</t>
+  </si>
+  <si>
+    <t>Senior Manager, Integrated Mobility Programs</t>
+  </si>
+  <si>
+    <t>Britepaths</t>
+  </si>
+  <si>
+    <t>USD 65000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Financial Literacy Personal Finance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/44653478944d4954952712fcd8f483aa-senior-manager-integrated-mobility-programs-britepaths-fairfax</t>
+  </si>
+  <si>
+    <t>Senior Project Manager, Performance</t>
+  </si>
+  <si>
+    <t>Partners for HOME</t>
+  </si>
+  <si>
+    <t>Atlanta, Georgia</t>
+  </si>
+  <si>
+    <t>USD 66000.00 - 84000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d64520fac0b64112a592404aedbd6f1a-senior-project-manager-performance-partners-for-home-atlanta</t>
+  </si>
+  <si>
+    <t>Senior Salesforce.com Implementation Specialist</t>
+  </si>
+  <si>
+    <t>Idlewild Partners, Inc.</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/e6611cd878ba4d1286c7067c0d2671d0-senior-salesforcecom-implementation-specialist-idlewild-partners-inc-downtown-brooklyn</t>
+  </si>
+  <si>
+    <t>downtown brooklyn, ny</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/a03d08ac64e948fabd93165b5a8efb95-senior-salesforcecom-implementation-specialist-idlewild-partners-inc-downtown-brooklyn</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/2728b87e665e4de7a255575dccd419e9-senior-salesforcecom-implementation-specialist-idlewild-partners-inc-downtown-brooklyn</t>
+  </si>
+  <si>
+    <t>Shelter Staff (Daytime Shift)</t>
+  </si>
+  <si>
+    <t>USD 19.00 - 20.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/97dc3123f6bf494ab9eb139db1ea81a4-shelter-staff-daytime-shift-sarahs-circle-chicago-chicago</t>
+  </si>
+  <si>
+    <t>Staff Attorney, Guardian ad Litem</t>
+  </si>
+  <si>
+    <t>Children's Law Center</t>
+  </si>
+  <si>
+    <t>USD 66000.00 - 76512.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/55761919679a4a82a897ac622a3fcd74-staff-attorney-guardian-ad-litem-childrens-law-center-washington</t>
+  </si>
+  <si>
+    <t>Supervising Attorney, Families Together</t>
+  </si>
+  <si>
+    <t>USD 82005.00 - 102302.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6b9a2ab160754a2796457704b1208441-supervising-attorney-families-together-childrens-law-center-washington</t>
+  </si>
+  <si>
+    <t>Teach English in Honduras (housing, benefits + stipend provided)</t>
+  </si>
+  <si>
+    <t>One Thousand Schools</t>
+  </si>
+  <si>
+    <t>El Progreso, Yoro Department, HN</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/27814b711c974cb2949dfd306a74ec21-teach-english-in-honduras-housing-benefits-stipend-provided-one-thousand-schools-el-progreso</t>
+  </si>
+  <si>
+    <t>Teaching Fellow/Teacher</t>
+  </si>
+  <si>
+    <t>City Teaching Alliance</t>
+  </si>
+  <si>
+    <t>Baltimore County, Maryland</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fb55d9c1ed4e45819475b9155eb3e23d-teaching-fellowteacher-city-teaching-alliance-baltimore-county</t>
+  </si>
+  <si>
+    <t>Dallas County, Texas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d94939c2c0fb4c6f8acf9104b7f92306-teaching-fellowteacher-city-teaching-alliance-dallas-county</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/43e94e39629b4eb3be769ca4959017b0-teaching-fellowteacher-city-teaching-alliance-philadelphia</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1feac4e6c099444e8a8a250248373302-teaching-fellowteacher-city-teaching-alliance-washington</t>
+  </si>
+  <si>
+    <t>Veterans' Legal Services Attorney</t>
+  </si>
+  <si>
+    <t>Montana Legal Services Association</t>
+  </si>
+  <si>
+    <t>Helena, MT</t>
+  </si>
+  <si>
+    <t>USD 68000.00 - 74000.00/year</t>
+  </si>
+  <si>
+    <t>Consumer Protection, Housing Homelessness, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/288abc3b360748faab698140dd205715-veterans-legal-services-attorney-montana-legal-services-association-helena</t>
+  </si>
+  <si>
+    <t>Website &amp; Data Analytics Associate</t>
+  </si>
+  <si>
+    <t>Mark Morris Dance Group</t>
+  </si>
+  <si>
+    <t>USD 46000.00 - 52000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/47aa85a7dd414f8680bb73386d1233b9-website-data-analytics-associate-mark-morris-dance-group-kings-county</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -54,6 +1698,10 @@
     </font>
     <font>
       <b/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF1155CC"/>
     </font>
   </fonts>
   <fills count="2">
@@ -76,9 +1724,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -418,7 +2067,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -457,8 +2106,610 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" t="s">
+        <v>55</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" t="s">
+        <v>60</v>
+      </c>
+      <c r="F10" t="s">
+        <v>61</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>63</v>
+      </c>
+      <c r="B11" t="s">
+        <v>64</v>
+      </c>
+      <c r="C11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D11" t="s">
+        <v>66</v>
+      </c>
+      <c r="E11" t="s">
+        <v>67</v>
+      </c>
+      <c r="F11" t="s">
+        <v>68</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>70</v>
+      </c>
+      <c r="B12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E12" t="s">
+        <v>72</v>
+      </c>
+      <c r="F12" t="s">
+        <v>61</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>74</v>
+      </c>
+      <c r="B13" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" t="s">
+        <v>71</v>
+      </c>
+      <c r="E13" t="s">
+        <v>75</v>
+      </c>
+      <c r="F13" t="s">
+        <v>61</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>77</v>
+      </c>
+      <c r="B14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" t="s">
+        <v>78</v>
+      </c>
+      <c r="D14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" t="s">
+        <v>79</v>
+      </c>
+      <c r="F14" t="s">
+        <v>80</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>82</v>
+      </c>
+      <c r="B15" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" t="s">
+        <v>83</v>
+      </c>
+      <c r="D15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" t="s">
+        <v>84</v>
+      </c>
+      <c r="F15" t="s">
+        <v>85</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" t="s">
+        <v>89</v>
+      </c>
+      <c r="D16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" t="s">
+        <v>90</v>
+      </c>
+      <c r="F16" t="s">
+        <v>91</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>93</v>
+      </c>
+      <c r="B17" t="s">
+        <v>94</v>
+      </c>
+      <c r="C17" t="s">
+        <v>95</v>
+      </c>
+      <c r="D17" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" t="s">
+        <v>96</v>
+      </c>
+      <c r="F17" t="s">
+        <v>97</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>99</v>
+      </c>
+      <c r="B18" t="s">
+        <v>88</v>
+      </c>
+      <c r="C18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D18" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" t="s">
+        <v>100</v>
+      </c>
+      <c r="F18" t="s">
+        <v>91</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>102</v>
+      </c>
+      <c r="B19" t="s">
+        <v>103</v>
+      </c>
+      <c r="C19" t="s">
+        <v>104</v>
+      </c>
+      <c r="D19" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" t="s">
+        <v>105</v>
+      </c>
+      <c r="F19" t="s">
+        <v>106</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>108</v>
+      </c>
+      <c r="B20" t="s">
+        <v>109</v>
+      </c>
+      <c r="C20" t="s">
+        <v>110</v>
+      </c>
+      <c r="D20" t="s">
+        <v>71</v>
+      </c>
+      <c r="E20" t="s">
+        <v>111</v>
+      </c>
+      <c r="F20" t="s">
+        <v>112</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>114</v>
+      </c>
+      <c r="B21" t="s">
+        <v>115</v>
+      </c>
+      <c r="C21" t="s">
+        <v>116</v>
+      </c>
+      <c r="D21" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" t="s">
+        <v>117</v>
+      </c>
+      <c r="F21" t="s">
+        <v>118</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>120</v>
+      </c>
+      <c r="B22" t="s">
+        <v>121</v>
+      </c>
+      <c r="C22" t="s">
+        <v>122</v>
+      </c>
+      <c r="D22" t="s">
+        <v>71</v>
+      </c>
+      <c r="E22" t="s">
+        <v>123</v>
+      </c>
+      <c r="F22" t="s">
+        <v>85</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>125</v>
+      </c>
+      <c r="B23" t="s">
+        <v>126</v>
+      </c>
+      <c r="C23" t="s">
+        <v>127</v>
+      </c>
+      <c r="D23" t="s">
+        <v>71</v>
+      </c>
+      <c r="E23" t="s">
+        <v>128</v>
+      </c>
+      <c r="F23" t="s">
+        <v>129</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>131</v>
+      </c>
+      <c r="B24" t="s">
+        <v>132</v>
+      </c>
+      <c r="C24" t="s">
+        <v>133</v>
+      </c>
+      <c r="D24" t="s">
+        <v>134</v>
+      </c>
+      <c r="E24" t="s">
+        <v>135</v>
+      </c>
+      <c r="F24" t="s">
+        <v>136</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>138</v>
+      </c>
+      <c r="B25" t="s">
+        <v>139</v>
+      </c>
+      <c r="C25" t="s">
+        <v>140</v>
+      </c>
+      <c r="D25" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" t="s">
+        <v>141</v>
+      </c>
+      <c r="F25" t="s">
+        <v>43</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>143</v>
+      </c>
+      <c r="B26" t="s">
+        <v>144</v>
+      </c>
+      <c r="C26" t="s">
+        <v>145</v>
+      </c>
+      <c r="D26" t="s">
+        <v>71</v>
+      </c>
+      <c r="E26" t="s">
+        <v>146</v>
+      </c>
+      <c r="F26" t="s">
+        <v>147</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -514,7 +2765,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H89"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -553,8 +2804,2122 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E2" t="s">
+        <v>153</v>
+      </c>
+      <c r="F2" t="s">
+        <v>154</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C3" t="s">
+        <v>158</v>
+      </c>
+      <c r="D3" t="s">
+        <v>159</v>
+      </c>
+      <c r="E3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C4" t="s">
+        <v>165</v>
+      </c>
+      <c r="D4" t="s">
+        <v>159</v>
+      </c>
+      <c r="E4" t="s">
+        <v>166</v>
+      </c>
+      <c r="F4" t="s">
+        <v>167</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B5" t="s">
+        <v>170</v>
+      </c>
+      <c r="C5" t="s">
+        <v>158</v>
+      </c>
+      <c r="D5" t="s">
+        <v>159</v>
+      </c>
+      <c r="E5" t="s">
+        <v>171</v>
+      </c>
+      <c r="F5" t="s">
+        <v>172</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B6" t="s">
+        <v>175</v>
+      </c>
+      <c r="C6" t="s">
+        <v>176</v>
+      </c>
+      <c r="D6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E6" t="s">
+        <v>177</v>
+      </c>
+      <c r="F6" t="s">
+        <v>178</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>180</v>
+      </c>
+      <c r="B7" t="s">
+        <v>181</v>
+      </c>
+      <c r="C7" t="s">
+        <v>182</v>
+      </c>
+      <c r="D7" t="s">
+        <v>159</v>
+      </c>
+      <c r="E7" t="s">
+        <v>183</v>
+      </c>
+      <c r="F7" t="s">
+        <v>184</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>186</v>
+      </c>
+      <c r="B8" t="s">
+        <v>187</v>
+      </c>
+      <c r="C8" t="s">
+        <v>188</v>
+      </c>
+      <c r="D8" t="s">
+        <v>159</v>
+      </c>
+      <c r="E8" t="s">
+        <v>189</v>
+      </c>
+      <c r="F8" t="s">
+        <v>190</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>192</v>
+      </c>
+      <c r="B9" t="s">
+        <v>193</v>
+      </c>
+      <c r="C9" t="s">
+        <v>158</v>
+      </c>
+      <c r="D9" t="s">
+        <v>159</v>
+      </c>
+      <c r="E9" t="s">
+        <v>194</v>
+      </c>
+      <c r="F9" t="s">
+        <v>195</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>197</v>
+      </c>
+      <c r="B10" t="s">
+        <v>198</v>
+      </c>
+      <c r="C10" t="s">
+        <v>199</v>
+      </c>
+      <c r="D10" t="s">
+        <v>159</v>
+      </c>
+      <c r="E10" t="s">
+        <v>200</v>
+      </c>
+      <c r="F10" t="s">
+        <v>201</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>203</v>
+      </c>
+      <c r="B11" t="s">
+        <v>204</v>
+      </c>
+      <c r="C11" t="s">
+        <v>205</v>
+      </c>
+      <c r="D11" t="s">
+        <v>159</v>
+      </c>
+      <c r="E11" t="s">
+        <v>206</v>
+      </c>
+      <c r="F11" t="s">
+        <v>207</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>209</v>
+      </c>
+      <c r="B12" t="s">
+        <v>210</v>
+      </c>
+      <c r="C12" t="s">
+        <v>165</v>
+      </c>
+      <c r="D12" t="s">
+        <v>159</v>
+      </c>
+      <c r="E12" t="s">
+        <v>211</v>
+      </c>
+      <c r="F12" t="s">
+        <v>212</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>214</v>
+      </c>
+      <c r="B13" t="s">
+        <v>215</v>
+      </c>
+      <c r="C13" t="s">
+        <v>216</v>
+      </c>
+      <c r="D13" t="s">
+        <v>159</v>
+      </c>
+      <c r="E13" t="s">
+        <v>217</v>
+      </c>
+      <c r="F13" t="s">
+        <v>218</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>220</v>
+      </c>
+      <c r="B14" t="s">
+        <v>221</v>
+      </c>
+      <c r="C14" t="s">
+        <v>158</v>
+      </c>
+      <c r="D14" t="s">
+        <v>159</v>
+      </c>
+      <c r="E14" t="s">
+        <v>222</v>
+      </c>
+      <c r="F14" t="s">
+        <v>223</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>225</v>
+      </c>
+      <c r="B15" t="s">
+        <v>226</v>
+      </c>
+      <c r="C15" t="s">
+        <v>227</v>
+      </c>
+      <c r="D15" t="s">
+        <v>228</v>
+      </c>
+      <c r="E15" t="s">
+        <v>229</v>
+      </c>
+      <c r="F15" t="s">
+        <v>230</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>232</v>
+      </c>
+      <c r="B16" t="s">
+        <v>233</v>
+      </c>
+      <c r="C16" t="s">
+        <v>188</v>
+      </c>
+      <c r="D16" t="s">
+        <v>159</v>
+      </c>
+      <c r="E16" t="s">
+        <v>234</v>
+      </c>
+      <c r="F16" t="s">
+        <v>235</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>237</v>
+      </c>
+      <c r="B17" t="s">
+        <v>238</v>
+      </c>
+      <c r="C17" t="s">
+        <v>151</v>
+      </c>
+      <c r="D17" t="s">
+        <v>159</v>
+      </c>
+      <c r="E17" t="s">
+        <v>239</v>
+      </c>
+      <c r="F17" t="s">
+        <v>240</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>242</v>
+      </c>
+      <c r="B18" t="s">
+        <v>243</v>
+      </c>
+      <c r="C18" t="s">
+        <v>244</v>
+      </c>
+      <c r="D18" t="s">
+        <v>159</v>
+      </c>
+      <c r="E18" t="s">
+        <v>245</v>
+      </c>
+      <c r="F18" t="s">
+        <v>246</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>248</v>
+      </c>
+      <c r="B19" t="s">
+        <v>249</v>
+      </c>
+      <c r="C19" t="s">
+        <v>188</v>
+      </c>
+      <c r="D19" t="s">
+        <v>159</v>
+      </c>
+      <c r="E19" t="s">
+        <v>250</v>
+      </c>
+      <c r="F19" t="s">
+        <v>167</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>252</v>
+      </c>
+      <c r="B20" t="s">
+        <v>253</v>
+      </c>
+      <c r="C20" t="s">
+        <v>188</v>
+      </c>
+      <c r="D20" t="s">
+        <v>159</v>
+      </c>
+      <c r="E20" t="s">
+        <v>254</v>
+      </c>
+      <c r="F20" t="s">
+        <v>255</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>257</v>
+      </c>
+      <c r="B21" t="s">
+        <v>258</v>
+      </c>
+      <c r="C21" t="s">
+        <v>259</v>
+      </c>
+      <c r="D21" t="s">
+        <v>159</v>
+      </c>
+      <c r="E21" t="s">
+        <v>260</v>
+      </c>
+      <c r="F21" t="s">
+        <v>261</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>263</v>
+      </c>
+      <c r="B22" t="s">
+        <v>264</v>
+      </c>
+      <c r="C22" t="s">
+        <v>265</v>
+      </c>
+      <c r="D22" t="s">
+        <v>159</v>
+      </c>
+      <c r="E22" t="s">
+        <v>266</v>
+      </c>
+      <c r="F22" t="s">
+        <v>267</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>269</v>
+      </c>
+      <c r="B23" t="s">
+        <v>270</v>
+      </c>
+      <c r="C23" t="s">
+        <v>271</v>
+      </c>
+      <c r="D23" t="s">
+        <v>159</v>
+      </c>
+      <c r="E23" t="s">
+        <v>272</v>
+      </c>
+      <c r="F23" t="s">
+        <v>154</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>274</v>
+      </c>
+      <c r="B24" t="s">
+        <v>275</v>
+      </c>
+      <c r="C24" t="s">
+        <v>188</v>
+      </c>
+      <c r="D24" t="s">
+        <v>159</v>
+      </c>
+      <c r="E24" t="s">
+        <v>276</v>
+      </c>
+      <c r="F24" t="s">
+        <v>277</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>279</v>
+      </c>
+      <c r="B25" t="s">
+        <v>280</v>
+      </c>
+      <c r="C25" t="s">
+        <v>188</v>
+      </c>
+      <c r="D25" t="s">
+        <v>152</v>
+      </c>
+      <c r="E25" t="s">
+        <v>281</v>
+      </c>
+      <c r="F25" t="s">
+        <v>282</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>284</v>
+      </c>
+      <c r="B26" t="s">
+        <v>285</v>
+      </c>
+      <c r="C26" t="s">
+        <v>244</v>
+      </c>
+      <c r="D26" t="s">
+        <v>159</v>
+      </c>
+      <c r="E26" t="s">
+        <v>286</v>
+      </c>
+      <c r="F26" t="s">
+        <v>287</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>289</v>
+      </c>
+      <c r="B27" t="s">
+        <v>215</v>
+      </c>
+      <c r="C27" t="s">
+        <v>216</v>
+      </c>
+      <c r="D27" t="s">
+        <v>290</v>
+      </c>
+      <c r="E27" t="s">
+        <v>291</v>
+      </c>
+      <c r="F27" t="s">
+        <v>218</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>293</v>
+      </c>
+      <c r="B28" t="s">
+        <v>294</v>
+      </c>
+      <c r="C28" t="s">
+        <v>295</v>
+      </c>
+      <c r="D28" t="s">
+        <v>159</v>
+      </c>
+      <c r="E28" t="s">
+        <v>296</v>
+      </c>
+      <c r="F28" t="s">
+        <v>297</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>293</v>
+      </c>
+      <c r="B29" t="s">
+        <v>299</v>
+      </c>
+      <c r="C29" t="s">
+        <v>265</v>
+      </c>
+      <c r="D29" t="s">
+        <v>159</v>
+      </c>
+      <c r="E29" t="s">
+        <v>167</v>
+      </c>
+      <c r="F29" t="s">
+        <v>300</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>302</v>
+      </c>
+      <c r="B30" t="s">
+        <v>303</v>
+      </c>
+      <c r="C30" t="s">
+        <v>304</v>
+      </c>
+      <c r="D30" t="s">
+        <v>159</v>
+      </c>
+      <c r="E30" t="s">
+        <v>305</v>
+      </c>
+      <c r="F30" t="s">
+        <v>306</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>308</v>
+      </c>
+      <c r="B31" t="s">
+        <v>215</v>
+      </c>
+      <c r="C31" t="s">
+        <v>216</v>
+      </c>
+      <c r="D31" t="s">
+        <v>159</v>
+      </c>
+      <c r="E31" t="s">
+        <v>309</v>
+      </c>
+      <c r="F31" t="s">
+        <v>218</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>311</v>
+      </c>
+      <c r="B32" t="s">
+        <v>312</v>
+      </c>
+      <c r="C32" t="s">
+        <v>313</v>
+      </c>
+      <c r="D32" t="s">
+        <v>159</v>
+      </c>
+      <c r="E32" t="s">
+        <v>314</v>
+      </c>
+      <c r="F32" t="s">
+        <v>315</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>317</v>
+      </c>
+      <c r="B33" t="s">
+        <v>318</v>
+      </c>
+      <c r="C33" t="s">
+        <v>158</v>
+      </c>
+      <c r="D33" t="s">
+        <v>159</v>
+      </c>
+      <c r="E33" t="s">
+        <v>167</v>
+      </c>
+      <c r="F33" t="s">
+        <v>319</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>321</v>
+      </c>
+      <c r="B34" t="s">
+        <v>322</v>
+      </c>
+      <c r="C34" t="s">
+        <v>265</v>
+      </c>
+      <c r="D34" t="s">
+        <v>159</v>
+      </c>
+      <c r="E34" t="s">
+        <v>323</v>
+      </c>
+      <c r="F34" t="s">
+        <v>324</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>326</v>
+      </c>
+      <c r="B35" t="s">
+        <v>327</v>
+      </c>
+      <c r="C35" t="s">
+        <v>165</v>
+      </c>
+      <c r="D35" t="s">
+        <v>290</v>
+      </c>
+      <c r="E35" t="s">
+        <v>328</v>
+      </c>
+      <c r="F35" t="s">
+        <v>329</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>331</v>
+      </c>
+      <c r="B36" t="s">
+        <v>332</v>
+      </c>
+      <c r="C36" t="s">
+        <v>333</v>
+      </c>
+      <c r="D36" t="s">
+        <v>159</v>
+      </c>
+      <c r="E36" t="s">
+        <v>334</v>
+      </c>
+      <c r="F36" t="s">
+        <v>335</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>337</v>
+      </c>
+      <c r="B37" t="s">
+        <v>338</v>
+      </c>
+      <c r="C37" t="s">
+        <v>158</v>
+      </c>
+      <c r="D37" t="s">
+        <v>159</v>
+      </c>
+      <c r="E37" t="s">
+        <v>339</v>
+      </c>
+      <c r="F37" t="s">
+        <v>340</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>342</v>
+      </c>
+      <c r="B38" t="s">
+        <v>343</v>
+      </c>
+      <c r="C38" t="s">
+        <v>344</v>
+      </c>
+      <c r="D38" t="s">
+        <v>159</v>
+      </c>
+      <c r="E38" t="s">
+        <v>345</v>
+      </c>
+      <c r="F38" t="s">
+        <v>346</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>348</v>
+      </c>
+      <c r="B39" t="s">
+        <v>349</v>
+      </c>
+      <c r="C39" t="s">
+        <v>350</v>
+      </c>
+      <c r="D39" t="s">
+        <v>159</v>
+      </c>
+      <c r="E39" t="s">
+        <v>351</v>
+      </c>
+      <c r="F39" t="s">
+        <v>352</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>354</v>
+      </c>
+      <c r="B40" t="s">
+        <v>355</v>
+      </c>
+      <c r="C40" t="s">
+        <v>356</v>
+      </c>
+      <c r="D40" t="s">
+        <v>159</v>
+      </c>
+      <c r="E40" t="s">
+        <v>357</v>
+      </c>
+      <c r="F40" t="s">
+        <v>319</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>359</v>
+      </c>
+      <c r="B41" t="s">
+        <v>275</v>
+      </c>
+      <c r="C41" t="s">
+        <v>188</v>
+      </c>
+      <c r="D41" t="s">
+        <v>159</v>
+      </c>
+      <c r="E41" t="s">
+        <v>360</v>
+      </c>
+      <c r="F41" t="s">
+        <v>277</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>362</v>
+      </c>
+      <c r="B42" t="s">
+        <v>170</v>
+      </c>
+      <c r="C42" t="s">
+        <v>158</v>
+      </c>
+      <c r="D42" t="s">
+        <v>159</v>
+      </c>
+      <c r="E42" t="s">
+        <v>363</v>
+      </c>
+      <c r="F42" t="s">
+        <v>364</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>366</v>
+      </c>
+      <c r="B43" t="s">
+        <v>367</v>
+      </c>
+      <c r="C43" t="s">
+        <v>368</v>
+      </c>
+      <c r="D43" t="s">
+        <v>159</v>
+      </c>
+      <c r="E43" t="s">
+        <v>167</v>
+      </c>
+      <c r="F43" t="s">
+        <v>212</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>370</v>
+      </c>
+      <c r="B44" t="s">
+        <v>371</v>
+      </c>
+      <c r="C44" t="s">
+        <v>372</v>
+      </c>
+      <c r="D44" t="s">
+        <v>290</v>
+      </c>
+      <c r="E44" t="s">
+        <v>373</v>
+      </c>
+      <c r="F44" t="s">
+        <v>167</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>375</v>
+      </c>
+      <c r="B45" t="s">
+        <v>376</v>
+      </c>
+      <c r="C45" t="s">
+        <v>265</v>
+      </c>
+      <c r="D45" t="s">
+        <v>290</v>
+      </c>
+      <c r="E45" t="s">
+        <v>167</v>
+      </c>
+      <c r="F45" t="s">
+        <v>261</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>378</v>
+      </c>
+      <c r="B46" t="s">
+        <v>379</v>
+      </c>
+      <c r="C46" t="s">
+        <v>356</v>
+      </c>
+      <c r="D46" t="s">
+        <v>159</v>
+      </c>
+      <c r="E46" t="s">
+        <v>380</v>
+      </c>
+      <c r="F46" t="s">
+        <v>235</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>382</v>
+      </c>
+      <c r="B47" t="s">
+        <v>379</v>
+      </c>
+      <c r="C47" t="s">
+        <v>383</v>
+      </c>
+      <c r="D47" t="s">
+        <v>159</v>
+      </c>
+      <c r="E47" t="s">
+        <v>380</v>
+      </c>
+      <c r="F47" t="s">
+        <v>235</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>385</v>
+      </c>
+      <c r="B48" t="s">
+        <v>379</v>
+      </c>
+      <c r="C48" t="s">
+        <v>386</v>
+      </c>
+      <c r="D48" t="s">
+        <v>159</v>
+      </c>
+      <c r="E48" t="s">
+        <v>380</v>
+      </c>
+      <c r="F48" t="s">
+        <v>235</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>388</v>
+      </c>
+      <c r="B49" t="s">
+        <v>389</v>
+      </c>
+      <c r="C49" t="s">
+        <v>390</v>
+      </c>
+      <c r="D49" t="s">
+        <v>159</v>
+      </c>
+      <c r="E49" t="s">
+        <v>167</v>
+      </c>
+      <c r="F49" t="s">
+        <v>391</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>393</v>
+      </c>
+      <c r="B50" t="s">
+        <v>394</v>
+      </c>
+      <c r="C50" t="s">
+        <v>395</v>
+      </c>
+      <c r="D50" t="s">
+        <v>159</v>
+      </c>
+      <c r="E50" t="s">
+        <v>183</v>
+      </c>
+      <c r="F50" t="s">
+        <v>396</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>87</v>
+      </c>
+      <c r="B51" t="s">
+        <v>215</v>
+      </c>
+      <c r="C51" t="s">
+        <v>216</v>
+      </c>
+      <c r="D51" t="s">
+        <v>159</v>
+      </c>
+      <c r="E51" t="s">
+        <v>398</v>
+      </c>
+      <c r="F51" t="s">
+        <v>218</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>400</v>
+      </c>
+      <c r="B52" t="s">
+        <v>401</v>
+      </c>
+      <c r="C52" t="s">
+        <v>265</v>
+      </c>
+      <c r="D52" t="s">
+        <v>152</v>
+      </c>
+      <c r="E52" t="s">
+        <v>402</v>
+      </c>
+      <c r="F52" t="s">
+        <v>403</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>405</v>
+      </c>
+      <c r="B53" t="s">
+        <v>406</v>
+      </c>
+      <c r="C53" t="s">
+        <v>158</v>
+      </c>
+      <c r="D53" t="s">
+        <v>290</v>
+      </c>
+      <c r="E53" t="s">
+        <v>407</v>
+      </c>
+      <c r="F53" t="s">
+        <v>408</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>410</v>
+      </c>
+      <c r="B54" t="s">
+        <v>411</v>
+      </c>
+      <c r="C54" t="s">
+        <v>265</v>
+      </c>
+      <c r="D54" t="s">
+        <v>290</v>
+      </c>
+      <c r="E54" t="s">
+        <v>373</v>
+      </c>
+      <c r="F54" t="s">
+        <v>412</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>414</v>
+      </c>
+      <c r="B55" t="s">
+        <v>415</v>
+      </c>
+      <c r="C55" t="s">
+        <v>416</v>
+      </c>
+      <c r="D55" t="s">
+        <v>228</v>
+      </c>
+      <c r="E55" t="s">
+        <v>417</v>
+      </c>
+      <c r="F55" t="s">
+        <v>167</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>419</v>
+      </c>
+      <c r="B56" t="s">
+        <v>420</v>
+      </c>
+      <c r="C56" t="s">
+        <v>165</v>
+      </c>
+      <c r="D56" t="s">
+        <v>159</v>
+      </c>
+      <c r="E56" t="s">
+        <v>421</v>
+      </c>
+      <c r="F56" t="s">
+        <v>422</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>424</v>
+      </c>
+      <c r="B57" t="s">
+        <v>264</v>
+      </c>
+      <c r="C57" t="s">
+        <v>265</v>
+      </c>
+      <c r="D57" t="s">
+        <v>159</v>
+      </c>
+      <c r="E57" t="s">
+        <v>425</v>
+      </c>
+      <c r="F57" t="s">
+        <v>267</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>427</v>
+      </c>
+      <c r="B58" t="s">
+        <v>428</v>
+      </c>
+      <c r="C58" t="s">
+        <v>429</v>
+      </c>
+      <c r="D58" t="s">
+        <v>159</v>
+      </c>
+      <c r="E58" t="s">
+        <v>430</v>
+      </c>
+      <c r="F58" t="s">
+        <v>431</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>433</v>
+      </c>
+      <c r="B59" t="s">
+        <v>428</v>
+      </c>
+      <c r="C59" t="s">
+        <v>429</v>
+      </c>
+      <c r="D59" t="s">
+        <v>159</v>
+      </c>
+      <c r="E59" t="s">
+        <v>430</v>
+      </c>
+      <c r="F59" t="s">
+        <v>434</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>436</v>
+      </c>
+      <c r="B60" t="s">
+        <v>437</v>
+      </c>
+      <c r="C60" t="s">
+        <v>158</v>
+      </c>
+      <c r="D60" t="s">
+        <v>159</v>
+      </c>
+      <c r="E60" t="s">
+        <v>438</v>
+      </c>
+      <c r="F60" t="s">
+        <v>439</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>441</v>
+      </c>
+      <c r="B61" t="s">
+        <v>442</v>
+      </c>
+      <c r="C61" t="s">
+        <v>158</v>
+      </c>
+      <c r="D61" t="s">
+        <v>159</v>
+      </c>
+      <c r="E61" t="s">
+        <v>443</v>
+      </c>
+      <c r="F61" t="s">
+        <v>444</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>446</v>
+      </c>
+      <c r="B62" t="s">
+        <v>215</v>
+      </c>
+      <c r="C62" t="s">
+        <v>216</v>
+      </c>
+      <c r="D62" t="s">
+        <v>159</v>
+      </c>
+      <c r="E62" t="s">
+        <v>447</v>
+      </c>
+      <c r="F62" t="s">
+        <v>218</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>449</v>
+      </c>
+      <c r="B63" t="s">
+        <v>450</v>
+      </c>
+      <c r="C63" t="s">
+        <v>451</v>
+      </c>
+      <c r="D63" t="s">
+        <v>159</v>
+      </c>
+      <c r="E63" t="s">
+        <v>452</v>
+      </c>
+      <c r="F63" t="s">
+        <v>453</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>455</v>
+      </c>
+      <c r="B64" t="s">
+        <v>456</v>
+      </c>
+      <c r="C64" t="s">
+        <v>188</v>
+      </c>
+      <c r="D64" t="s">
+        <v>290</v>
+      </c>
+      <c r="E64" t="s">
+        <v>457</v>
+      </c>
+      <c r="F64" t="s">
+        <v>261</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>459</v>
+      </c>
+      <c r="B65" t="s">
+        <v>460</v>
+      </c>
+      <c r="C65" t="s">
+        <v>461</v>
+      </c>
+      <c r="D65" t="s">
+        <v>152</v>
+      </c>
+      <c r="E65" t="s">
+        <v>167</v>
+      </c>
+      <c r="F65" t="s">
+        <v>462</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>464</v>
+      </c>
+      <c r="B66" t="s">
+        <v>465</v>
+      </c>
+      <c r="C66" t="s">
+        <v>466</v>
+      </c>
+      <c r="D66" t="s">
+        <v>159</v>
+      </c>
+      <c r="E66" t="s">
+        <v>467</v>
+      </c>
+      <c r="F66" t="s">
+        <v>468</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>470</v>
+      </c>
+      <c r="B67" t="s">
+        <v>465</v>
+      </c>
+      <c r="C67" t="s">
+        <v>471</v>
+      </c>
+      <c r="D67" t="s">
+        <v>159</v>
+      </c>
+      <c r="E67" t="s">
+        <v>467</v>
+      </c>
+      <c r="F67" t="s">
+        <v>468</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>473</v>
+      </c>
+      <c r="B68" t="s">
+        <v>474</v>
+      </c>
+      <c r="C68" t="s">
+        <v>344</v>
+      </c>
+      <c r="D68" t="s">
+        <v>159</v>
+      </c>
+      <c r="E68" t="s">
+        <v>475</v>
+      </c>
+      <c r="F68" t="s">
+        <v>476</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>478</v>
+      </c>
+      <c r="B69" t="s">
+        <v>479</v>
+      </c>
+      <c r="C69" t="s">
+        <v>480</v>
+      </c>
+      <c r="D69" t="s">
+        <v>159</v>
+      </c>
+      <c r="E69" t="s">
+        <v>481</v>
+      </c>
+      <c r="F69" t="s">
+        <v>482</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>484</v>
+      </c>
+      <c r="B70" t="s">
+        <v>479</v>
+      </c>
+      <c r="C70" t="s">
+        <v>485</v>
+      </c>
+      <c r="D70" t="s">
+        <v>159</v>
+      </c>
+      <c r="E70" t="s">
+        <v>481</v>
+      </c>
+      <c r="F70" t="s">
+        <v>482</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>487</v>
+      </c>
+      <c r="B71" t="s">
+        <v>474</v>
+      </c>
+      <c r="C71" t="s">
+        <v>188</v>
+      </c>
+      <c r="D71" t="s">
+        <v>159</v>
+      </c>
+      <c r="E71" t="s">
+        <v>488</v>
+      </c>
+      <c r="F71" t="s">
+        <v>476</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>490</v>
+      </c>
+      <c r="B72" t="s">
+        <v>491</v>
+      </c>
+      <c r="C72" t="s">
+        <v>265</v>
+      </c>
+      <c r="D72" t="s">
+        <v>159</v>
+      </c>
+      <c r="E72" t="s">
+        <v>492</v>
+      </c>
+      <c r="F72" t="s">
+        <v>493</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>495</v>
+      </c>
+      <c r="B73" t="s">
+        <v>496</v>
+      </c>
+      <c r="C73" t="s">
+        <v>265</v>
+      </c>
+      <c r="D73" t="s">
+        <v>159</v>
+      </c>
+      <c r="E73" t="s">
+        <v>497</v>
+      </c>
+      <c r="F73" t="s">
+        <v>498</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>500</v>
+      </c>
+      <c r="B74" t="s">
+        <v>501</v>
+      </c>
+      <c r="C74" t="s">
+        <v>344</v>
+      </c>
+      <c r="D74" t="s">
+        <v>159</v>
+      </c>
+      <c r="E74" t="s">
+        <v>167</v>
+      </c>
+      <c r="F74" t="s">
+        <v>167</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>503</v>
+      </c>
+      <c r="B75" t="s">
+        <v>504</v>
+      </c>
+      <c r="C75" t="s">
+        <v>265</v>
+      </c>
+      <c r="D75" t="s">
+        <v>159</v>
+      </c>
+      <c r="E75" t="s">
+        <v>505</v>
+      </c>
+      <c r="F75" t="s">
+        <v>506</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>508</v>
+      </c>
+      <c r="B76" t="s">
+        <v>509</v>
+      </c>
+      <c r="C76" t="s">
+        <v>510</v>
+      </c>
+      <c r="D76" t="s">
+        <v>159</v>
+      </c>
+      <c r="E76" t="s">
+        <v>511</v>
+      </c>
+      <c r="F76" t="s">
+        <v>512</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>514</v>
+      </c>
+      <c r="B77" t="s">
+        <v>515</v>
+      </c>
+      <c r="C77" t="s">
+        <v>265</v>
+      </c>
+      <c r="D77" t="s">
+        <v>159</v>
+      </c>
+      <c r="E77" t="s">
+        <v>516</v>
+      </c>
+      <c r="F77" t="s">
+        <v>167</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>514</v>
+      </c>
+      <c r="B78" t="s">
+        <v>515</v>
+      </c>
+      <c r="C78" t="s">
+        <v>518</v>
+      </c>
+      <c r="D78" t="s">
+        <v>159</v>
+      </c>
+      <c r="E78" t="s">
+        <v>516</v>
+      </c>
+      <c r="F78" t="s">
+        <v>167</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>514</v>
+      </c>
+      <c r="B79" t="s">
+        <v>515</v>
+      </c>
+      <c r="C79" t="s">
+        <v>265</v>
+      </c>
+      <c r="D79" t="s">
+        <v>159</v>
+      </c>
+      <c r="E79" t="s">
+        <v>516</v>
+      </c>
+      <c r="F79" t="s">
+        <v>167</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>521</v>
+      </c>
+      <c r="B80" t="s">
+        <v>243</v>
+      </c>
+      <c r="C80" t="s">
+        <v>244</v>
+      </c>
+      <c r="D80" t="s">
+        <v>159</v>
+      </c>
+      <c r="E80" t="s">
+        <v>522</v>
+      </c>
+      <c r="F80" t="s">
+        <v>246</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>524</v>
+      </c>
+      <c r="B81" t="s">
+        <v>525</v>
+      </c>
+      <c r="C81" t="s">
+        <v>188</v>
+      </c>
+      <c r="D81" t="s">
+        <v>159</v>
+      </c>
+      <c r="E81" t="s">
+        <v>526</v>
+      </c>
+      <c r="F81" t="s">
+        <v>527</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>529</v>
+      </c>
+      <c r="B82" t="s">
+        <v>525</v>
+      </c>
+      <c r="C82" t="s">
+        <v>188</v>
+      </c>
+      <c r="D82" t="s">
+        <v>159</v>
+      </c>
+      <c r="E82" t="s">
+        <v>530</v>
+      </c>
+      <c r="F82" t="s">
+        <v>527</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>532</v>
+      </c>
+      <c r="B83" t="s">
+        <v>533</v>
+      </c>
+      <c r="C83" t="s">
+        <v>534</v>
+      </c>
+      <c r="D83" t="s">
+        <v>159</v>
+      </c>
+      <c r="E83" t="s">
+        <v>167</v>
+      </c>
+      <c r="F83" t="s">
+        <v>535</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>537</v>
+      </c>
+      <c r="B84" t="s">
+        <v>538</v>
+      </c>
+      <c r="C84" t="s">
+        <v>539</v>
+      </c>
+      <c r="D84" t="s">
+        <v>159</v>
+      </c>
+      <c r="E84" t="s">
+        <v>540</v>
+      </c>
+      <c r="F84" t="s">
+        <v>154</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>537</v>
+      </c>
+      <c r="B85" t="s">
+        <v>538</v>
+      </c>
+      <c r="C85" t="s">
+        <v>542</v>
+      </c>
+      <c r="D85" t="s">
+        <v>159</v>
+      </c>
+      <c r="E85" t="s">
+        <v>540</v>
+      </c>
+      <c r="F85" t="s">
+        <v>154</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>537</v>
+      </c>
+      <c r="B86" t="s">
+        <v>538</v>
+      </c>
+      <c r="C86" t="s">
+        <v>368</v>
+      </c>
+      <c r="D86" t="s">
+        <v>159</v>
+      </c>
+      <c r="E86" t="s">
+        <v>540</v>
+      </c>
+      <c r="F86" t="s">
+        <v>154</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>537</v>
+      </c>
+      <c r="B87" t="s">
+        <v>538</v>
+      </c>
+      <c r="C87" t="s">
+        <v>188</v>
+      </c>
+      <c r="D87" t="s">
+        <v>159</v>
+      </c>
+      <c r="E87" t="s">
+        <v>540</v>
+      </c>
+      <c r="F87" t="s">
+        <v>154</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>546</v>
+      </c>
+      <c r="B88" t="s">
+        <v>547</v>
+      </c>
+      <c r="C88" t="s">
+        <v>548</v>
+      </c>
+      <c r="D88" t="s">
+        <v>159</v>
+      </c>
+      <c r="E88" t="s">
+        <v>549</v>
+      </c>
+      <c r="F88" t="s">
+        <v>550</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>552</v>
+      </c>
+      <c r="B89" t="s">
+        <v>553</v>
+      </c>
+      <c r="C89" t="s">
+        <v>271</v>
+      </c>
+      <c r="D89" t="s">
+        <v>159</v>
+      </c>
+      <c r="E89" t="s">
+        <v>554</v>
+      </c>
+      <c r="F89" t="s">
+        <v>412</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>555</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+    <hyperlink ref="H59" r:id="rId58"/>
+    <hyperlink ref="H60" r:id="rId59"/>
+    <hyperlink ref="H61" r:id="rId60"/>
+    <hyperlink ref="H62" r:id="rId61"/>
+    <hyperlink ref="H63" r:id="rId62"/>
+    <hyperlink ref="H64" r:id="rId63"/>
+    <hyperlink ref="H65" r:id="rId64"/>
+    <hyperlink ref="H66" r:id="rId65"/>
+    <hyperlink ref="H67" r:id="rId66"/>
+    <hyperlink ref="H68" r:id="rId67"/>
+    <hyperlink ref="H69" r:id="rId68"/>
+    <hyperlink ref="H70" r:id="rId69"/>
+    <hyperlink ref="H71" r:id="rId70"/>
+    <hyperlink ref="H72" r:id="rId71"/>
+    <hyperlink ref="H73" r:id="rId72"/>
+    <hyperlink ref="H74" r:id="rId73"/>
+    <hyperlink ref="H75" r:id="rId74"/>
+    <hyperlink ref="H76" r:id="rId75"/>
+    <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/xlsx/jobs-2026-10-30.xlsx
+++ b/docs/xlsx/jobs-2026-10-30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="556">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="683">
   <si>
     <t>Title</t>
   </si>
@@ -538,6 +538,39 @@
     <t>https://www.idealist.org/en/nonprofit-job/602780447b164b5fbf43a42186d4641a-assistant-general-counsel-hadassah-wzoa-inc-new-york</t>
   </si>
   <si>
+    <t>Associate Director of Institutional Partnerships</t>
+  </si>
+  <si>
+    <t>Summer Search</t>
+  </si>
+  <si>
+    <t>Seattle, Washington</t>
+  </si>
+  <si>
+    <t>USD 104731.00 - 113118.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a903cb714fec41d68d1eb3387295c5ed-associate-director-of-institutional-partnerships-summer-search-seattle</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/87ea9f2699fd4844b5208d4156fa0b9b-associate-director-of-institutional-partnerships-summer-search-oakland</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/415522aaa3cd402f8a900fb6d4f2074e-associate-director-of-institutional-partnerships-summer-search-boston</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/367ab31c2ce74751a6bc8132ba357dbb-associate-director-of-institutional-partnerships-summer-search-new-york</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0ca1dbc1911349b1aeff436569060b78-associate-director-of-institutional-partnerships-summer-search-philadelphia</t>
+  </si>
+  <si>
     <t>Bilingual Content Creator</t>
   </si>
   <si>
@@ -556,6 +589,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/b01db8baedab4fcc963f2841578b8f9a-bilingual-content-creator-siembra-nc-raleigh</t>
   </si>
   <si>
+    <t>Business Analyst / Strategy, Funding &amp; Operations - Chennai Only</t>
+  </si>
+  <si>
+    <t>Empower Tamizhagam</t>
+  </si>
+  <si>
+    <t>Chennai, Tamil Nadu, IN</t>
+  </si>
+  <si>
+    <t>INR 30000.00 - 50000.00/month</t>
+  </si>
+  <si>
+    <t>Economic Development, Community Development, Entrepreneurship</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/edb6996056624979a01bcb2b0c2a6a2f-business-analyst-strategy-funding-operations-chennai-only-empower-tamizhagam-chennai</t>
+  </si>
+  <si>
     <t>Case Manager</t>
   </si>
   <si>
@@ -574,6 +625,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/b74b8474113545b2bc533b305e51b5bc-case-manager-beautiful-day-granola-providence</t>
   </si>
   <si>
+    <t>Jewish Association Serving the Aging</t>
+  </si>
+  <si>
+    <t>Brooklyn, New York</t>
+  </si>
+  <si>
+    <t>USD 30.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/647ae80742f64b07ab07e2a7b4fe893f-case-manager-jewish-association-serving-the-aging-brooklyn</t>
+  </si>
+  <si>
     <t>Chief Executive Officer (CEO)</t>
   </si>
   <si>
@@ -670,12 +733,24 @@
     <t>USD 50000.00 - 60000.00/year</t>
   </si>
   <si>
-    <t>Children Youth, Education</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/e7081c21d5ba42bbaafc4bcaef2e31d3-community-recruiter-small-magic-birmingham</t>
   </si>
   <si>
+    <t>Consulting Services Associate</t>
+  </si>
+  <si>
+    <t>Partners for Sacred Places</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>Community Development, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/818e4a4693a8473e921674ff96171663-consulting-services-associate-partners-for-sacred-places-chicago</t>
+  </si>
+  <si>
     <t>Coordinator, Programs and Events</t>
   </si>
   <si>
@@ -691,6 +766,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/3874267206fc4582ae5286d09e62bb58-coordinator-programs-and-events-new-york-genealogical-biographical-society-new-york</t>
   </si>
   <si>
+    <t>Deputy Executive Director</t>
+  </si>
+  <si>
+    <t>ART FOR THE JOURNEY</t>
+  </si>
+  <si>
+    <t>Richmond, Virginia</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Community Development, Veterans</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/779f4e9b51114ab3956ab25ef159e929-deputy-executive-director-art-for-the-journey-richmond</t>
+  </si>
+  <si>
     <t>Development Associate - Temporary</t>
   </si>
   <si>
@@ -712,6 +805,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/cf3dbf1fca124c15ac476a15a02778b4-development-associate-temporary-selt-southeast-land-trust-of-new-hampshire-epping</t>
   </si>
   <si>
+    <t>Development Coordinator (CRS)</t>
+  </si>
+  <si>
+    <t>Congregation Rodeph Sholom &amp; Rodeph Sholom School</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f4193e1125a647f38694cddaf19ec6cf-development-coordinator-crs-congregation-rodeph-sholom-rodeph-sholom-school-new-york</t>
+  </si>
+  <si>
     <t>Digital Communications Strategist</t>
   </si>
   <si>
@@ -748,9 +856,6 @@
     <t>Sarah's Circle (Chicago)</t>
   </si>
   <si>
-    <t>Chicago, Illinois</t>
-  </si>
-  <si>
     <t>USD 86000.00 - 108000.00/year</t>
   </si>
   <si>
@@ -823,6 +928,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/d6e2dceae2954b7b89f4fbef8673d45e-director-of-finance-protect-democracy-washington</t>
   </si>
   <si>
+    <t>Director of Human Resources</t>
+  </si>
+  <si>
+    <t>Young Women's Freedom Center</t>
+  </si>
+  <si>
+    <t>USD 130000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2f14ce7cbb2f4360ad210b3b143ab662-director-of-human-resources-young-womens-freedom-center-oakland</t>
+  </si>
+  <si>
     <t>Director of Operations, OAC</t>
   </si>
   <si>
@@ -868,6 +988,36 @@
     <t>https://www.idealist.org/en/job/5a437eb42383476d8d4ef223a09180eb-donor-operations-coordinator-the-choice-inc-washington</t>
   </si>
   <si>
+    <t>Engagement &amp; Advocacy Coordinator</t>
+  </si>
+  <si>
+    <t>Community Energy Project</t>
+  </si>
+  <si>
+    <t>Portland, Oregon</t>
+  </si>
+  <si>
+    <t>USD 64085.00 - 64085.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d8417efad6fa471393d8109183ed6d99-engagement-advocacy-coordinator-community-energy-project-portland</t>
+  </si>
+  <si>
+    <t>Events &amp; Donor Engagement Manager</t>
+  </si>
+  <si>
+    <t>Fiver Children's Foundation</t>
+  </si>
+  <si>
+    <t>USD 72000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a1e5eef8809d4f3aa16b89c031902c03-events-donor-engagement-manager-fiver-childrens-foundation-new-york</t>
+  </si>
+  <si>
     <t>Executive Administrative Assistant</t>
   </si>
   <si>
@@ -922,6 +1072,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/7d9c569810ae47ecb6dbd938d4191619-executive-director-appendix-cancer-pmp-research-foundation-springfield</t>
   </si>
   <si>
+    <t>Retreat Farm, Ltd.</t>
+  </si>
+  <si>
+    <t>Brattleboro, Vermont</t>
+  </si>
+  <si>
+    <t>USD 125000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Rural Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4b6a6870183a4313be46e2575dbaa0a0-executive-director-retreat-farm-ltd-brattleboro</t>
+  </si>
+  <si>
     <t>Executive Director / CEO</t>
   </si>
   <si>
@@ -967,6 +1132,42 @@
     <t>https://www.idealist.org/en/nonprofit-job/5803b25e16b34831a9440fddcfe65b68-family-law-attorney-south-asian-network-san-artesia</t>
   </si>
   <si>
+    <t>Finance and Grants Specialist</t>
+  </si>
+  <si>
+    <t>Safe Alternatives to Violent Environments</t>
+  </si>
+  <si>
+    <t>Fremont, California</t>
+  </si>
+  <si>
+    <t>USD 77750.00 - 77750.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ed1a97a213be4cae9fab4d8f3f4e83a3-finance-and-grants-specialist-safe-alternatives-to-violent-environments-fremont</t>
+  </si>
+  <si>
+    <t>Fundraising Coordinator</t>
+  </si>
+  <si>
+    <t>Neurofibromatosis Northeast</t>
+  </si>
+  <si>
+    <t>Burlington, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 27.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d719b0c3ac6c4c2e90c399487c6b61d7-fundraising-coordinator-neurofibromatosis-northeast-burlington</t>
+  </si>
+  <si>
     <t>Grants Administrator (Research Programs Specialist) - Office of Research &amp; Sponsored Programs</t>
   </si>
   <si>
@@ -979,6 +1180,36 @@
     <t>https://www.idealist.org/en/job/596a64abb9584ca2bbb485852ab133e5-grants-administrator-research-programs-specialist-office-of-research-sponsored-programs-the-graduate-center-cuny-new-york</t>
   </si>
   <si>
+    <t>Grants Coordinator</t>
+  </si>
+  <si>
+    <t>Pisgah Legal Services</t>
+  </si>
+  <si>
+    <t>Asheville, North Carolina</t>
+  </si>
+  <si>
+    <t>USD 49471.00 - 86890.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/1546454ae16f424cb4f596bf39a84e3e-grants-coordinator-pisgah-legal-services-asheville</t>
+  </si>
+  <si>
+    <t>Housing Support Specialist (Rental Assistance)</t>
+  </si>
+  <si>
+    <t>Defy Ventures</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>Economic Development, Job Workplace, Entrepreneurship</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c72da9e6c2db4f7383943a309347bde8-housing-support-specialist-rental-assistance-defy-ventures-los-angeles</t>
+  </si>
+  <si>
     <t>HR Manager</t>
   </si>
   <si>
@@ -1066,9 +1297,6 @@
     <t>California Center for Movement Legal Services</t>
   </si>
   <si>
-    <t>Los Angeles, California</t>
-  </si>
-  <si>
     <t>USD 54000.00 - 58000.00/year</t>
   </si>
   <si>
@@ -1078,6 +1306,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/e3e14db7d9e6467ba84e929c016f909e-legal-assistant-california-center-for-movement-legal-services-los-angeles</t>
   </si>
   <si>
+    <t>Legal Assistant - Remote *Anywhere USA*</t>
+  </si>
+  <si>
+    <t>Compassion and Choices</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e818a9d0d06c409e863f9c129b393c7a-legal-assistant-remote-anywhere-usa-compassion-and-choices-washington</t>
+  </si>
+  <si>
     <t>Major Gift Officer - West Coast</t>
   </si>
   <si>
@@ -1093,6 +1333,33 @@
     <t>https://www.idealist.org/en/nonprofit-job/2a7e980b9ffb4e68ae1f7af3b42a4357-major-gift-officer-west-coast-national-outdoor-leadership-school-nols-lander</t>
   </si>
   <si>
+    <t>Manager of Communications and Outreach</t>
+  </si>
+  <si>
+    <t>RUNX1 Research Program</t>
+  </si>
+  <si>
+    <t>Health Medicine, Philanthropy, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/de16175fc6c1485eba31d4aa2a995d65-manager-of-communications-and-outreach-runx1-research-program-santa-barbara</t>
+  </si>
+  <si>
+    <t>Manager of Participant Support LMSW/LCSW/LMHC (Advance + Earn)</t>
+  </si>
+  <si>
+    <t>Goddard Riverside Community Center</t>
+  </si>
+  <si>
+    <t>USD 71000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/92a35947088941b6adf4a2402eba3548-manager-of-participant-support-lmswlcswlmhc-advance-earn-goddard-riverside-community-center-new-york</t>
+  </si>
+  <si>
     <t>Manager, Donor Engagement</t>
   </si>
   <si>
@@ -1114,15 +1381,27 @@
     <t>https://www.idealist.org/en/nonprofit-job/6d5dfa8587da408bad6ce4d221ce3bd5-manager-philanthropy-reporting-and-projects-hadassah-wzoa-inc-new-york</t>
   </si>
   <si>
+    <t>Manager, Summer Math Enrichment</t>
+  </si>
+  <si>
+    <t>The Art of Problem Solving Initiative, Inc.</t>
+  </si>
+  <si>
+    <t>USD 66000.00 - 78375.00/year</t>
+  </si>
+  <si>
+    <t>Education, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4c9cc13a997f49519288cc7c616919ae-manager-summer-math-enrichment-the-art-of-problem-solving-initiative-inc-los-angeles</t>
+  </si>
+  <si>
     <t>Market Program Coordinator, Fairhill (Bilingual English/Spanish)</t>
   </si>
   <si>
     <t>Small Things, Inc.</t>
   </si>
   <si>
-    <t>Philadelphia, Pennsylvania</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/e9fd3874e8a44082a9146948c2e51860-market-program-coordinator-fairhill-bilingual-englishspanish-small-things-inc-philadelphia</t>
   </si>
   <si>
@@ -1153,9 +1432,6 @@
     <t>Movement Manager - Remote California</t>
   </si>
   <si>
-    <t>Compassion and Choices</t>
-  </si>
-  <si>
     <t>USD 80000.00 - 95000.00/year</t>
   </si>
   <si>
@@ -1216,6 +1492,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/3249d3d67ed249d9baed61a359968dab-operations-coordinator-small-magic-birmingham</t>
   </si>
   <si>
+    <t>National Black Theatre</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 26.00/hour</t>
+  </si>
+  <si>
+    <t>Arts Music, Entrepreneurship, Race Ethnicity</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2fb890f40dc1495dba295902ae325bd2-operations-coordinator-national-black-theatre-new-york</t>
+  </si>
+  <si>
     <t>Outreach Coordinator</t>
   </si>
   <si>
@@ -1234,15 +1522,9 @@
     <t>Part-Time After School Elementary Math Educator</t>
   </si>
   <si>
-    <t>The Art of Problem Solving Initiative, Inc.</t>
-  </si>
-  <si>
     <t>USD 40.00 - 40.00/hour</t>
   </si>
   <si>
-    <t>Education, Children Youth</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/79a7bb62acc14889a4e378053c6468e4-part-time-after-school-elementary-math-educator-the-art-of-problem-solving-initiative-inc-new-york</t>
   </si>
   <si>
@@ -1288,6 +1570,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/473fe19a3631463a8b532ee5146d845e-philanthropic-advisor-combined-jewish-philanthropies-boston</t>
   </si>
   <si>
+    <t>President</t>
+  </si>
+  <si>
+    <t>Amazon Conservation Association</t>
+  </si>
+  <si>
+    <t>Agriculture, Environment, International Relations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/44ab9c0b2cf04cb9aa5296da0532f02c-president-amazon-conservation-association-washington</t>
+  </si>
+  <si>
     <t>Principal Giving Officer</t>
   </si>
   <si>
@@ -1324,6 +1618,33 @@
     <t>https://www.idealist.org/en/nonprofit-job/87c0b00de18342dcaf756ded6423231c-program-assistant-energy-employees-unit-cpwr-the-center-for-construction-research-and-training-silver-spring</t>
   </si>
   <si>
+    <t>Program Associate, Higher Education</t>
+  </si>
+  <si>
+    <t>Active Minds</t>
+  </si>
+  <si>
+    <t>USD 52500.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3cfbd563811e435ab3bdba5e8abbe70e-program-associate-higher-education-active-minds-washington</t>
+  </si>
+  <si>
+    <t>Program Coordinator (Full-Time)</t>
+  </si>
+  <si>
+    <t>National Council of Jewish Women, NY Section</t>
+  </si>
+  <si>
+    <t>Poverty, Seniors Retirement, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9c0b91a690884a818e71a4f3a10e6f32-program-coordinator-full-time-national-council-of-jewish-women-ny-section-new-york</t>
+  </si>
+  <si>
     <t>Program Coordinator, Learning, Culture &amp; Community</t>
   </si>
   <si>
@@ -1435,6 +1756,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/807e18d0768f4459abb81e7def6c4d58-public-defender-client-advocate-in-san-fernando-ca-partners-for-justice-san-fernando</t>
   </si>
   <si>
+    <t>Receptionist</t>
+  </si>
+  <si>
+    <t>Habeas Corpus Resource Center</t>
+  </si>
+  <si>
+    <t>USD 4365.00 - 4365.00/month</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Legal Assistance, Prison Reform</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/3f9abb9f2ba34911b5533cc6cb2de2fc-receptionist-habeas-corpus-resource-center-san-francisco</t>
+  </si>
+  <si>
     <t>Regional Associate, Northwest</t>
   </si>
   <si>
@@ -1486,15 +1822,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/5d58e1fc685b463e8616dc1f3df4d021-relationship-manager-dc-maryland-and-virginia-j-street-washington</t>
   </si>
   <si>
+    <t>Renewable Northwest Executive Director</t>
+  </si>
+  <si>
+    <t>Clover Search Works</t>
+  </si>
+  <si>
+    <t>USD 190000.00 - 220000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/d9fd3560ced640f3a8fc9272c932a249-renewable-northwest-executive-director-clover-search-works-portland</t>
+  </si>
+  <si>
     <t>Salesforce Administrator and Business Analyst</t>
   </si>
   <si>
     <t>Wilshire Boulevard Temple</t>
   </si>
   <si>
-    <t>USD 75000.00 - 85000.00/year</t>
-  </si>
-  <si>
     <t>Religion Spirituality</t>
   </si>
   <si>
@@ -1516,6 +1861,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/1e69da5b0cb24ad1ac4e764343d6d1ad-senior-advisor-affiliate-legal-programs-american-civil-liberties-union-new-york</t>
   </si>
   <si>
+    <t>Senior Associate, Policy</t>
+  </si>
+  <si>
+    <t>American Public Human Services Association</t>
+  </si>
+  <si>
+    <t>USD 76500.00 - 86500.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/060c9e5e5b2643c89bc85a0844d7b703-senior-associate-policy-american-public-human-services-association-arlington</t>
+  </si>
+  <si>
     <t>Senior Employment Law Attorney</t>
   </si>
   <si>
@@ -1540,6 +1897,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/44653478944d4954952712fcd8f483aa-senior-manager-integrated-mobility-programs-britepaths-fairfax</t>
   </si>
   <si>
+    <t>Senior Manager, Partnerships and Engagement (California)</t>
+  </si>
+  <si>
+    <t>The Doug Flutie, Jr. Foundation for Autism, Inc.</t>
+  </si>
+  <si>
+    <t>Children Youth, Disability, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9923078d24b143119ca1a0b251a18842-senior-manager-partnerships-and-engagement-california-the-doug-flutie-jr-foundation-for-autism-inc-los-angeles</t>
+  </si>
+  <si>
     <t>Senior Project Manager, Performance</t>
   </si>
   <si>
@@ -1652,6 +2021,18 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/1feac4e6c099444e8a8a250248373302-teaching-fellowteacher-city-teaching-alliance-washington</t>
+  </si>
+  <si>
+    <t>Trainer</t>
+  </si>
+  <si>
+    <t>The Posse Foundation, Bay Area</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2cc36dfdb6434ff38c70711d7e6bf036-trainer-the-posse-foundation-bay-area-san-francisco</t>
   </si>
   <si>
     <t>Veterans' Legal Services Attorney</t>
@@ -2765,7 +3146,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H89"/>
+  <dimension ref="A1:H120"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -2921,56 +3302,56 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>174</v>
+      </c>
+      <c r="B7" t="s">
+        <v>175</v>
+      </c>
+      <c r="C7" t="s">
+        <v>151</v>
+      </c>
+      <c r="D7" t="s">
+        <v>159</v>
+      </c>
+      <c r="E7" t="s">
+        <v>177</v>
+      </c>
+      <c r="F7" t="s">
+        <v>178</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>180</v>
-      </c>
-      <c r="B7" t="s">
-        <v>181</v>
-      </c>
-      <c r="C7" t="s">
-        <v>182</v>
-      </c>
-      <c r="D7" t="s">
-        <v>159</v>
-      </c>
-      <c r="E7" t="s">
-        <v>183</v>
-      </c>
-      <c r="F7" t="s">
-        <v>184</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="B8" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="C8" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="D8" t="s">
         <v>159</v>
       </c>
       <c r="E8" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="F8" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="B9" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="C9" t="s">
         <v>158</v>
@@ -2979,921 +3360,921 @@
         <v>159</v>
       </c>
       <c r="E9" t="s">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c r="F9" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>197</v>
+        <v>174</v>
       </c>
       <c r="B10" t="s">
-        <v>198</v>
+        <v>175</v>
       </c>
       <c r="C10" t="s">
-        <v>199</v>
+        <v>183</v>
       </c>
       <c r="D10" t="s">
         <v>159</v>
       </c>
       <c r="E10" t="s">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="F10" t="s">
-        <v>201</v>
+        <v>178</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>202</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="B11" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="C11" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="D11" t="s">
         <v>159</v>
       </c>
       <c r="E11" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="F11" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="B12" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
       <c r="C12" t="s">
-        <v>165</v>
+        <v>193</v>
       </c>
       <c r="D12" t="s">
         <v>159</v>
       </c>
       <c r="E12" t="s">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="F12" t="s">
-        <v>212</v>
+        <v>195</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>213</v>
+        <v>196</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>214</v>
+        <v>197</v>
       </c>
       <c r="B13" t="s">
-        <v>215</v>
+        <v>198</v>
       </c>
       <c r="C13" t="s">
-        <v>216</v>
+        <v>199</v>
       </c>
       <c r="D13" t="s">
         <v>159</v>
       </c>
       <c r="E13" t="s">
-        <v>217</v>
+        <v>200</v>
       </c>
       <c r="F13" t="s">
-        <v>218</v>
+        <v>201</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>219</v>
+        <v>202</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>220</v>
+        <v>197</v>
       </c>
       <c r="B14" t="s">
-        <v>221</v>
+        <v>203</v>
       </c>
       <c r="C14" t="s">
-        <v>158</v>
+        <v>204</v>
       </c>
       <c r="D14" t="s">
         <v>159</v>
       </c>
       <c r="E14" t="s">
-        <v>222</v>
+        <v>205</v>
       </c>
       <c r="F14" t="s">
-        <v>223</v>
+        <v>167</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>224</v>
+        <v>206</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>225</v>
+        <v>207</v>
       </c>
       <c r="B15" t="s">
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="C15" t="s">
-        <v>227</v>
+        <v>209</v>
       </c>
       <c r="D15" t="s">
-        <v>228</v>
+        <v>159</v>
       </c>
       <c r="E15" t="s">
-        <v>229</v>
+        <v>210</v>
       </c>
       <c r="F15" t="s">
-        <v>230</v>
+        <v>211</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>231</v>
+        <v>212</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>232</v>
+        <v>213</v>
       </c>
       <c r="B16" t="s">
-        <v>233</v>
+        <v>214</v>
       </c>
       <c r="C16" t="s">
-        <v>188</v>
+        <v>158</v>
       </c>
       <c r="D16" t="s">
         <v>159</v>
       </c>
       <c r="E16" t="s">
-        <v>234</v>
+        <v>215</v>
       </c>
       <c r="F16" t="s">
-        <v>235</v>
+        <v>216</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>236</v>
+        <v>217</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>237</v>
+        <v>218</v>
       </c>
       <c r="B17" t="s">
-        <v>238</v>
+        <v>219</v>
       </c>
       <c r="C17" t="s">
-        <v>151</v>
+        <v>220</v>
       </c>
       <c r="D17" t="s">
         <v>159</v>
       </c>
       <c r="E17" t="s">
-        <v>239</v>
+        <v>221</v>
       </c>
       <c r="F17" t="s">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>241</v>
+        <v>223</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>242</v>
+        <v>224</v>
       </c>
       <c r="B18" t="s">
-        <v>243</v>
+        <v>225</v>
       </c>
       <c r="C18" t="s">
-        <v>244</v>
+        <v>226</v>
       </c>
       <c r="D18" t="s">
         <v>159</v>
       </c>
       <c r="E18" t="s">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="F18" t="s">
-        <v>246</v>
+        <v>228</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>247</v>
+        <v>229</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>248</v>
+        <v>230</v>
       </c>
       <c r="B19" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="C19" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="D19" t="s">
         <v>159</v>
       </c>
       <c r="E19" t="s">
-        <v>250</v>
+        <v>232</v>
       </c>
       <c r="F19" t="s">
-        <v>167</v>
+        <v>233</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="B20" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
       <c r="C20" t="s">
-        <v>188</v>
+        <v>237</v>
       </c>
       <c r="D20" t="s">
         <v>159</v>
       </c>
       <c r="E20" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="F20" t="s">
-        <v>255</v>
+        <v>178</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>256</v>
+        <v>239</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="B21" t="s">
-        <v>258</v>
+        <v>241</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>242</v>
       </c>
       <c r="D21" t="s">
         <v>159</v>
       </c>
       <c r="E21" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
       <c r="F21" t="s">
-        <v>261</v>
+        <v>243</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>262</v>
+        <v>244</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>263</v>
+        <v>245</v>
       </c>
       <c r="B22" t="s">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="C22" t="s">
-        <v>265</v>
+        <v>158</v>
       </c>
       <c r="D22" t="s">
         <v>159</v>
       </c>
       <c r="E22" t="s">
-        <v>266</v>
+        <v>247</v>
       </c>
       <c r="F22" t="s">
-        <v>267</v>
+        <v>248</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>268</v>
+        <v>249</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="B23" t="s">
-        <v>270</v>
+        <v>251</v>
       </c>
       <c r="C23" t="s">
-        <v>271</v>
+        <v>252</v>
       </c>
       <c r="D23" t="s">
         <v>159</v>
       </c>
       <c r="E23" t="s">
-        <v>272</v>
+        <v>253</v>
       </c>
       <c r="F23" t="s">
-        <v>154</v>
+        <v>254</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>273</v>
+        <v>255</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>274</v>
+        <v>256</v>
       </c>
       <c r="B24" t="s">
-        <v>275</v>
+        <v>257</v>
       </c>
       <c r="C24" t="s">
-        <v>188</v>
+        <v>258</v>
       </c>
       <c r="D24" t="s">
-        <v>159</v>
+        <v>259</v>
       </c>
       <c r="E24" t="s">
-        <v>276</v>
+        <v>260</v>
       </c>
       <c r="F24" t="s">
-        <v>277</v>
+        <v>261</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>278</v>
+        <v>262</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>279</v>
+        <v>263</v>
       </c>
       <c r="B25" t="s">
-        <v>280</v>
+        <v>264</v>
       </c>
       <c r="C25" t="s">
-        <v>188</v>
+        <v>158</v>
       </c>
       <c r="D25" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E25" t="s">
-        <v>281</v>
+        <v>265</v>
       </c>
       <c r="F25" t="s">
-        <v>282</v>
+        <v>266</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>284</v>
+        <v>268</v>
       </c>
       <c r="B26" t="s">
-        <v>285</v>
+        <v>269</v>
       </c>
       <c r="C26" t="s">
-        <v>244</v>
+        <v>209</v>
       </c>
       <c r="D26" t="s">
         <v>159</v>
       </c>
       <c r="E26" t="s">
-        <v>286</v>
+        <v>270</v>
       </c>
       <c r="F26" t="s">
-        <v>287</v>
+        <v>271</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>288</v>
+        <v>272</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>289</v>
+        <v>273</v>
       </c>
       <c r="B27" t="s">
-        <v>215</v>
+        <v>274</v>
       </c>
       <c r="C27" t="s">
-        <v>216</v>
+        <v>151</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>159</v>
       </c>
       <c r="E27" t="s">
-        <v>291</v>
+        <v>275</v>
       </c>
       <c r="F27" t="s">
-        <v>218</v>
+        <v>276</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>292</v>
+        <v>277</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>293</v>
+        <v>278</v>
       </c>
       <c r="B28" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="C28" t="s">
-        <v>295</v>
+        <v>242</v>
       </c>
       <c r="D28" t="s">
         <v>159</v>
       </c>
       <c r="E28" t="s">
-        <v>296</v>
+        <v>280</v>
       </c>
       <c r="F28" t="s">
-        <v>297</v>
+        <v>281</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>298</v>
+        <v>282</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="B29" t="s">
-        <v>299</v>
+        <v>284</v>
       </c>
       <c r="C29" t="s">
-        <v>265</v>
+        <v>209</v>
       </c>
       <c r="D29" t="s">
         <v>159</v>
       </c>
       <c r="E29" t="s">
+        <v>285</v>
+      </c>
+      <c r="F29" t="s">
         <v>167</v>
       </c>
-      <c r="F29" t="s">
-        <v>300</v>
-      </c>
       <c r="H29" s="2" t="s">
-        <v>301</v>
+        <v>286</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="B30" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="C30" t="s">
-        <v>304</v>
+        <v>209</v>
       </c>
       <c r="D30" t="s">
         <v>159</v>
       </c>
       <c r="E30" t="s">
-        <v>305</v>
+        <v>289</v>
       </c>
       <c r="F30" t="s">
-        <v>306</v>
+        <v>290</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>307</v>
+        <v>291</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>308</v>
+        <v>292</v>
       </c>
       <c r="B31" t="s">
-        <v>215</v>
+        <v>293</v>
       </c>
       <c r="C31" t="s">
-        <v>216</v>
+        <v>294</v>
       </c>
       <c r="D31" t="s">
         <v>159</v>
       </c>
       <c r="E31" t="s">
-        <v>309</v>
+        <v>295</v>
       </c>
       <c r="F31" t="s">
-        <v>218</v>
+        <v>296</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>310</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>311</v>
+        <v>298</v>
       </c>
       <c r="B32" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="C32" t="s">
-        <v>313</v>
+        <v>300</v>
       </c>
       <c r="D32" t="s">
         <v>159</v>
       </c>
       <c r="E32" t="s">
-        <v>314</v>
+        <v>301</v>
       </c>
       <c r="F32" t="s">
-        <v>315</v>
+        <v>302</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>316</v>
+        <v>303</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>317</v>
+        <v>304</v>
       </c>
       <c r="B33" t="s">
-        <v>318</v>
+        <v>305</v>
       </c>
       <c r="C33" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D33" t="s">
         <v>159</v>
       </c>
       <c r="E33" t="s">
-        <v>167</v>
+        <v>306</v>
       </c>
       <c r="F33" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="B34" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="C34" t="s">
-        <v>265</v>
+        <v>311</v>
       </c>
       <c r="D34" t="s">
         <v>159</v>
       </c>
       <c r="E34" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="F34" t="s">
-        <v>324</v>
+        <v>154</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="B35" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="C35" t="s">
-        <v>165</v>
+        <v>209</v>
       </c>
       <c r="D35" t="s">
-        <v>290</v>
+        <v>159</v>
       </c>
       <c r="E35" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="F35" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="B36" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="C36" t="s">
-        <v>333</v>
+        <v>209</v>
       </c>
       <c r="D36" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="E36" t="s">
-        <v>334</v>
+        <v>321</v>
       </c>
       <c r="F36" t="s">
-        <v>335</v>
+        <v>322</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>336</v>
+        <v>323</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>337</v>
+        <v>324</v>
       </c>
       <c r="B37" t="s">
-        <v>338</v>
+        <v>325</v>
       </c>
       <c r="C37" t="s">
-        <v>158</v>
+        <v>326</v>
       </c>
       <c r="D37" t="s">
         <v>159</v>
       </c>
       <c r="E37" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="F37" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="B38" t="s">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="C38" t="s">
-        <v>344</v>
+        <v>158</v>
       </c>
       <c r="D38" t="s">
         <v>159</v>
       </c>
       <c r="E38" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="F38" t="s">
-        <v>346</v>
+        <v>296</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>347</v>
+        <v>333</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>348</v>
+        <v>334</v>
       </c>
       <c r="B39" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="C39" t="s">
-        <v>350</v>
+        <v>242</v>
       </c>
       <c r="D39" t="s">
         <v>159</v>
       </c>
       <c r="E39" t="s">
-        <v>351</v>
+        <v>336</v>
       </c>
       <c r="F39" t="s">
-        <v>352</v>
+        <v>337</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>353</v>
+        <v>338</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>354</v>
+        <v>339</v>
       </c>
       <c r="B40" t="s">
-        <v>355</v>
+        <v>236</v>
       </c>
       <c r="C40" t="s">
-        <v>356</v>
+        <v>237</v>
       </c>
       <c r="D40" t="s">
-        <v>159</v>
+        <v>340</v>
       </c>
       <c r="E40" t="s">
-        <v>357</v>
+        <v>341</v>
       </c>
       <c r="F40" t="s">
-        <v>319</v>
+        <v>178</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>358</v>
+        <v>342</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>359</v>
+        <v>343</v>
       </c>
       <c r="B41" t="s">
-        <v>275</v>
+        <v>344</v>
       </c>
       <c r="C41" t="s">
-        <v>188</v>
+        <v>345</v>
       </c>
       <c r="D41" t="s">
         <v>159</v>
       </c>
       <c r="E41" t="s">
-        <v>360</v>
+        <v>346</v>
       </c>
       <c r="F41" t="s">
-        <v>277</v>
+        <v>347</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>361</v>
+        <v>348</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>362</v>
+        <v>343</v>
       </c>
       <c r="B42" t="s">
-        <v>170</v>
+        <v>349</v>
       </c>
       <c r="C42" t="s">
-        <v>158</v>
+        <v>300</v>
       </c>
       <c r="D42" t="s">
         <v>159</v>
       </c>
       <c r="E42" t="s">
-        <v>363</v>
+        <v>167</v>
       </c>
       <c r="F42" t="s">
-        <v>364</v>
+        <v>350</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>365</v>
+        <v>351</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>366</v>
+        <v>343</v>
       </c>
       <c r="B43" t="s">
-        <v>367</v>
+        <v>352</v>
       </c>
       <c r="C43" t="s">
-        <v>368</v>
+        <v>353</v>
       </c>
       <c r="D43" t="s">
         <v>159</v>
       </c>
       <c r="E43" t="s">
-        <v>167</v>
+        <v>354</v>
       </c>
       <c r="F43" t="s">
-        <v>212</v>
+        <v>355</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>370</v>
+        <v>357</v>
       </c>
       <c r="B44" t="s">
-        <v>371</v>
+        <v>358</v>
       </c>
       <c r="C44" t="s">
-        <v>372</v>
+        <v>359</v>
       </c>
       <c r="D44" t="s">
-        <v>290</v>
+        <v>159</v>
       </c>
       <c r="E44" t="s">
-        <v>373</v>
+        <v>360</v>
       </c>
       <c r="F44" t="s">
-        <v>167</v>
+        <v>361</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>374</v>
+        <v>362</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>375</v>
+        <v>363</v>
       </c>
       <c r="B45" t="s">
-        <v>376</v>
+        <v>236</v>
       </c>
       <c r="C45" t="s">
-        <v>265</v>
+        <v>237</v>
       </c>
       <c r="D45" t="s">
-        <v>290</v>
+        <v>159</v>
       </c>
       <c r="E45" t="s">
-        <v>167</v>
+        <v>364</v>
       </c>
       <c r="F45" t="s">
-        <v>261</v>
+        <v>178</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>377</v>
+        <v>365</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="B46" t="s">
-        <v>379</v>
+        <v>367</v>
       </c>
       <c r="C46" t="s">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c r="D46" t="s">
         <v>159</v>
       </c>
       <c r="E46" t="s">
-        <v>380</v>
+        <v>369</v>
       </c>
       <c r="F46" t="s">
-        <v>235</v>
+        <v>370</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="B47" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="C47" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="D47" t="s">
         <v>159</v>
       </c>
       <c r="E47" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="F47" t="s">
-        <v>235</v>
+        <v>376</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="B48" t="s">
         <v>379</v>
       </c>
       <c r="C48" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="D48" t="s">
-        <v>159</v>
+        <v>340</v>
       </c>
       <c r="E48" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F48" t="s">
-        <v>235</v>
+        <v>382</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="B49" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="C49" t="s">
-        <v>390</v>
+        <v>158</v>
       </c>
       <c r="D49" t="s">
         <v>159</v>
@@ -3902,119 +4283,119 @@
         <v>167</v>
       </c>
       <c r="F49" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="B50" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="C50" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="D50" t="s">
         <v>159</v>
       </c>
       <c r="E50" t="s">
-        <v>183</v>
+        <v>391</v>
       </c>
       <c r="F50" t="s">
-        <v>396</v>
+        <v>167</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>87</v>
+        <v>393</v>
       </c>
       <c r="B51" t="s">
-        <v>215</v>
+        <v>394</v>
       </c>
       <c r="C51" t="s">
-        <v>216</v>
+        <v>395</v>
       </c>
       <c r="D51" t="s">
         <v>159</v>
       </c>
       <c r="E51" t="s">
-        <v>398</v>
+        <v>381</v>
       </c>
       <c r="F51" t="s">
-        <v>218</v>
+        <v>396</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>398</v>
+      </c>
+      <c r="B52" t="s">
+        <v>399</v>
+      </c>
+      <c r="C52" t="s">
+        <v>300</v>
+      </c>
+      <c r="D52" t="s">
+        <v>159</v>
+      </c>
+      <c r="E52" t="s">
         <v>400</v>
       </c>
-      <c r="B52" t="s">
+      <c r="F52" t="s">
         <v>401</v>
       </c>
-      <c r="C52" t="s">
-        <v>265</v>
-      </c>
-      <c r="D52" t="s">
-        <v>152</v>
-      </c>
-      <c r="E52" t="s">
+      <c r="H52" s="2" t="s">
         <v>402</v>
-      </c>
-      <c r="F52" t="s">
-        <v>403</v>
-      </c>
-      <c r="H52" s="2" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>403</v>
+      </c>
+      <c r="B53" t="s">
+        <v>404</v>
+      </c>
+      <c r="C53" t="s">
+        <v>165</v>
+      </c>
+      <c r="D53" t="s">
+        <v>340</v>
+      </c>
+      <c r="E53" t="s">
         <v>405</v>
       </c>
-      <c r="B53" t="s">
+      <c r="F53" t="s">
         <v>406</v>
       </c>
-      <c r="C53" t="s">
-        <v>158</v>
-      </c>
-      <c r="D53" t="s">
-        <v>290</v>
-      </c>
-      <c r="E53" t="s">
+      <c r="H53" s="2" t="s">
         <v>407</v>
-      </c>
-      <c r="F53" t="s">
-        <v>408</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>408</v>
+      </c>
+      <c r="B54" t="s">
+        <v>409</v>
+      </c>
+      <c r="C54" t="s">
         <v>410</v>
       </c>
-      <c r="B54" t="s">
+      <c r="D54" t="s">
+        <v>159</v>
+      </c>
+      <c r="E54" t="s">
         <v>411</v>
-      </c>
-      <c r="C54" t="s">
-        <v>265</v>
-      </c>
-      <c r="D54" t="s">
-        <v>290</v>
-      </c>
-      <c r="E54" t="s">
-        <v>373</v>
       </c>
       <c r="F54" t="s">
         <v>412</v>
@@ -4031,16 +4412,16 @@
         <v>415</v>
       </c>
       <c r="C55" t="s">
+        <v>158</v>
+      </c>
+      <c r="D55" t="s">
+        <v>159</v>
+      </c>
+      <c r="E55" t="s">
         <v>416</v>
       </c>
-      <c r="D55" t="s">
-        <v>228</v>
-      </c>
-      <c r="E55" t="s">
+      <c r="F55" t="s">
         <v>417</v>
-      </c>
-      <c r="F55" t="s">
-        <v>167</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>418</v>
@@ -4054,119 +4435,119 @@
         <v>420</v>
       </c>
       <c r="C56" t="s">
-        <v>165</v>
+        <v>421</v>
       </c>
       <c r="D56" t="s">
         <v>159</v>
       </c>
       <c r="E56" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F56" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B57" t="s">
-        <v>264</v>
+        <v>426</v>
       </c>
       <c r="C57" t="s">
-        <v>265</v>
+        <v>395</v>
       </c>
       <c r="D57" t="s">
         <v>159</v>
       </c>
       <c r="E57" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="F57" t="s">
-        <v>267</v>
+        <v>428</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="B58" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C58" t="s">
-        <v>429</v>
+        <v>300</v>
       </c>
       <c r="D58" t="s">
         <v>159</v>
       </c>
       <c r="E58" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F58" t="s">
-        <v>431</v>
+        <v>271</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B59" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="C59" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="D59" t="s">
         <v>159</v>
       </c>
       <c r="E59" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="F59" t="s">
-        <v>434</v>
+        <v>386</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="B60" t="s">
+        <v>440</v>
+      </c>
+      <c r="C60" t="s">
+        <v>300</v>
+      </c>
+      <c r="D60" t="s">
+        <v>159</v>
+      </c>
+      <c r="E60" t="s">
         <v>437</v>
       </c>
-      <c r="C60" t="s">
-        <v>158</v>
-      </c>
-      <c r="D60" t="s">
-        <v>159</v>
-      </c>
-      <c r="E60" t="s">
-        <v>438</v>
-      </c>
       <c r="F60" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B61" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C61" t="s">
         <v>158</v>
@@ -4175,47 +4556,47 @@
         <v>159</v>
       </c>
       <c r="E61" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="F61" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B62" t="s">
-        <v>215</v>
+        <v>315</v>
       </c>
       <c r="C62" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="D62" t="s">
         <v>159</v>
       </c>
       <c r="E62" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="F62" t="s">
-        <v>218</v>
+        <v>317</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B63" t="s">
-        <v>450</v>
+        <v>170</v>
       </c>
       <c r="C63" t="s">
-        <v>451</v>
+        <v>158</v>
       </c>
       <c r="D63" t="s">
         <v>159</v>
@@ -4238,594 +4619,1307 @@
         <v>456</v>
       </c>
       <c r="C64" t="s">
-        <v>188</v>
+        <v>395</v>
       </c>
       <c r="D64" t="s">
-        <v>290</v>
+        <v>159</v>
       </c>
       <c r="E64" t="s">
         <v>457</v>
       </c>
       <c r="F64" t="s">
-        <v>261</v>
+        <v>458</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B65" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C65" t="s">
-        <v>461</v>
+        <v>183</v>
       </c>
       <c r="D65" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="E65" t="s">
         <v>167</v>
       </c>
       <c r="F65" t="s">
+        <v>233</v>
+      </c>
+      <c r="H65" s="2" t="s">
         <v>462</v>
-      </c>
-      <c r="H65" s="2" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>463</v>
+      </c>
+      <c r="B66" t="s">
         <v>464</v>
       </c>
-      <c r="B66" t="s">
+      <c r="C66" t="s">
         <v>465</v>
       </c>
-      <c r="C66" t="s">
+      <c r="D66" t="s">
+        <v>340</v>
+      </c>
+      <c r="E66" t="s">
         <v>466</v>
       </c>
-      <c r="D66" t="s">
-        <v>159</v>
-      </c>
-      <c r="E66" t="s">
+      <c r="F66" t="s">
+        <v>167</v>
+      </c>
+      <c r="H66" s="2" t="s">
         <v>467</v>
-      </c>
-      <c r="F66" t="s">
-        <v>468</v>
-      </c>
-      <c r="H66" s="2" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>468</v>
+      </c>
+      <c r="B67" t="s">
+        <v>469</v>
+      </c>
+      <c r="C67" t="s">
+        <v>300</v>
+      </c>
+      <c r="D67" t="s">
+        <v>340</v>
+      </c>
+      <c r="E67" t="s">
+        <v>167</v>
+      </c>
+      <c r="F67" t="s">
+        <v>296</v>
+      </c>
+      <c r="H67" s="2" t="s">
         <v>470</v>
-      </c>
-      <c r="B67" t="s">
-        <v>465</v>
-      </c>
-      <c r="C67" t="s">
-        <v>471</v>
-      </c>
-      <c r="D67" t="s">
-        <v>159</v>
-      </c>
-      <c r="E67" t="s">
-        <v>467</v>
-      </c>
-      <c r="F67" t="s">
-        <v>468</v>
-      </c>
-      <c r="H67" s="2" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>471</v>
+      </c>
+      <c r="B68" t="s">
+        <v>431</v>
+      </c>
+      <c r="C68" t="s">
+        <v>436</v>
+      </c>
+      <c r="D68" t="s">
+        <v>159</v>
+      </c>
+      <c r="E68" t="s">
+        <v>472</v>
+      </c>
+      <c r="F68" t="s">
+        <v>271</v>
+      </c>
+      <c r="H68" s="2" t="s">
         <v>473</v>
-      </c>
-      <c r="B68" t="s">
-        <v>474</v>
-      </c>
-      <c r="C68" t="s">
-        <v>344</v>
-      </c>
-      <c r="D68" t="s">
-        <v>159</v>
-      </c>
-      <c r="E68" t="s">
-        <v>475</v>
-      </c>
-      <c r="F68" t="s">
-        <v>476</v>
-      </c>
-      <c r="H68" s="2" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="B69" t="s">
-        <v>479</v>
+        <v>431</v>
       </c>
       <c r="C69" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="D69" t="s">
         <v>159</v>
       </c>
       <c r="E69" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
       <c r="F69" t="s">
-        <v>482</v>
+        <v>271</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="B70" t="s">
+        <v>431</v>
+      </c>
+      <c r="C70" t="s">
+        <v>478</v>
+      </c>
+      <c r="D70" t="s">
+        <v>159</v>
+      </c>
+      <c r="E70" t="s">
+        <v>472</v>
+      </c>
+      <c r="F70" t="s">
+        <v>271</v>
+      </c>
+      <c r="H70" s="2" t="s">
         <v>479</v>
-      </c>
-      <c r="C70" t="s">
-        <v>485</v>
-      </c>
-      <c r="D70" t="s">
-        <v>159</v>
-      </c>
-      <c r="E70" t="s">
-        <v>481</v>
-      </c>
-      <c r="F70" t="s">
-        <v>482</v>
-      </c>
-      <c r="H70" s="2" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="B71" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="C71" t="s">
-        <v>188</v>
+        <v>482</v>
       </c>
       <c r="D71" t="s">
         <v>159</v>
       </c>
       <c r="E71" t="s">
-        <v>488</v>
+        <v>167</v>
       </c>
       <c r="F71" t="s">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="B72" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="C72" t="s">
-        <v>265</v>
+        <v>487</v>
       </c>
       <c r="D72" t="s">
         <v>159</v>
       </c>
       <c r="E72" t="s">
-        <v>492</v>
+        <v>200</v>
       </c>
       <c r="F72" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>495</v>
+        <v>87</v>
       </c>
       <c r="B73" t="s">
-        <v>496</v>
+        <v>236</v>
       </c>
       <c r="C73" t="s">
-        <v>265</v>
+        <v>237</v>
       </c>
       <c r="D73" t="s">
         <v>159</v>
       </c>
       <c r="E73" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="F73" t="s">
-        <v>498</v>
+        <v>178</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>500</v>
+        <v>87</v>
       </c>
       <c r="B74" t="s">
-        <v>501</v>
+        <v>492</v>
       </c>
       <c r="C74" t="s">
-        <v>344</v>
+        <v>158</v>
       </c>
       <c r="D74" t="s">
         <v>159</v>
       </c>
       <c r="E74" t="s">
-        <v>167</v>
+        <v>493</v>
       </c>
       <c r="F74" t="s">
-        <v>167</v>
+        <v>494</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="B75" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="C75" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="D75" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="E75" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="F75" t="s">
-        <v>506</v>
+        <v>499</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="B76" t="s">
-        <v>509</v>
+        <v>456</v>
       </c>
       <c r="C76" t="s">
-        <v>510</v>
+        <v>158</v>
       </c>
       <c r="D76" t="s">
-        <v>159</v>
+        <v>340</v>
       </c>
       <c r="E76" t="s">
-        <v>511</v>
+        <v>502</v>
       </c>
       <c r="F76" t="s">
-        <v>512</v>
+        <v>458</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>513</v>
+        <v>503</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>514</v>
+        <v>504</v>
       </c>
       <c r="B77" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="C77" t="s">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="D77" t="s">
-        <v>159</v>
+        <v>340</v>
       </c>
       <c r="E77" t="s">
-        <v>516</v>
+        <v>466</v>
       </c>
       <c r="F77" t="s">
-        <v>167</v>
+        <v>506</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>517</v>
+        <v>507</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="B78" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="C78" t="s">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="D78" t="s">
-        <v>159</v>
+        <v>259</v>
       </c>
       <c r="E78" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="F78" t="s">
         <v>167</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>513</v>
+      </c>
+      <c r="B79" t="s">
         <v>514</v>
       </c>
-      <c r="B79" t="s">
+      <c r="C79" t="s">
+        <v>165</v>
+      </c>
+      <c r="D79" t="s">
+        <v>159</v>
+      </c>
+      <c r="E79" t="s">
         <v>515</v>
       </c>
-      <c r="C79" t="s">
-        <v>265</v>
-      </c>
-      <c r="D79" t="s">
-        <v>159</v>
-      </c>
-      <c r="E79" t="s">
+      <c r="F79" t="s">
         <v>516</v>
       </c>
-      <c r="F79" t="s">
-        <v>167</v>
-      </c>
       <c r="H79" s="2" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>518</v>
+      </c>
+      <c r="B80" t="s">
+        <v>519</v>
+      </c>
+      <c r="C80" t="s">
+        <v>209</v>
+      </c>
+      <c r="D80" t="s">
+        <v>159</v>
+      </c>
+      <c r="E80" t="s">
+        <v>167</v>
+      </c>
+      <c r="F80" t="s">
+        <v>520</v>
+      </c>
+      <c r="H80" s="2" t="s">
         <v>521</v>
-      </c>
-      <c r="B80" t="s">
-        <v>243</v>
-      </c>
-      <c r="C80" t="s">
-        <v>244</v>
-      </c>
-      <c r="D80" t="s">
-        <v>159</v>
-      </c>
-      <c r="E80" t="s">
-        <v>522</v>
-      </c>
-      <c r="F80" t="s">
-        <v>246</v>
-      </c>
-      <c r="H80" s="2" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
+        <v>522</v>
+      </c>
+      <c r="B81" t="s">
+        <v>299</v>
+      </c>
+      <c r="C81" t="s">
+        <v>300</v>
+      </c>
+      <c r="D81" t="s">
+        <v>159</v>
+      </c>
+      <c r="E81" t="s">
+        <v>523</v>
+      </c>
+      <c r="F81" t="s">
+        <v>302</v>
+      </c>
+      <c r="H81" s="2" t="s">
         <v>524</v>
-      </c>
-      <c r="B81" t="s">
-        <v>525</v>
-      </c>
-      <c r="C81" t="s">
-        <v>188</v>
-      </c>
-      <c r="D81" t="s">
-        <v>159</v>
-      </c>
-      <c r="E81" t="s">
-        <v>526</v>
-      </c>
-      <c r="F81" t="s">
-        <v>527</v>
-      </c>
-      <c r="H81" s="2" t="s">
-        <v>528</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>525</v>
+      </c>
+      <c r="B82" t="s">
+        <v>526</v>
+      </c>
+      <c r="C82" t="s">
+        <v>527</v>
+      </c>
+      <c r="D82" t="s">
+        <v>159</v>
+      </c>
+      <c r="E82" t="s">
+        <v>528</v>
+      </c>
+      <c r="F82" t="s">
         <v>529</v>
       </c>
-      <c r="B82" t="s">
-        <v>525</v>
-      </c>
-      <c r="C82" t="s">
-        <v>188</v>
-      </c>
-      <c r="D82" t="s">
-        <v>159</v>
-      </c>
-      <c r="E82" t="s">
+      <c r="H82" s="2" t="s">
         <v>530</v>
-      </c>
-      <c r="F82" t="s">
-        <v>527</v>
-      </c>
-      <c r="H82" s="2" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>531</v>
+      </c>
+      <c r="B83" t="s">
+        <v>526</v>
+      </c>
+      <c r="C83" t="s">
+        <v>527</v>
+      </c>
+      <c r="D83" t="s">
+        <v>159</v>
+      </c>
+      <c r="E83" t="s">
+        <v>528</v>
+      </c>
+      <c r="F83" t="s">
         <v>532</v>
       </c>
-      <c r="B83" t="s">
+      <c r="H83" s="2" t="s">
         <v>533</v>
-      </c>
-      <c r="C83" t="s">
-        <v>534</v>
-      </c>
-      <c r="D83" t="s">
-        <v>159</v>
-      </c>
-      <c r="E83" t="s">
-        <v>167</v>
-      </c>
-      <c r="F83" t="s">
-        <v>535</v>
-      </c>
-      <c r="H83" s="2" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
+        <v>534</v>
+      </c>
+      <c r="B84" t="s">
+        <v>535</v>
+      </c>
+      <c r="C84" t="s">
+        <v>300</v>
+      </c>
+      <c r="D84" t="s">
+        <v>159</v>
+      </c>
+      <c r="E84" t="s">
+        <v>536</v>
+      </c>
+      <c r="F84" t="s">
         <v>537</v>
       </c>
-      <c r="B84" t="s">
+      <c r="H84" s="2" t="s">
         <v>538</v>
-      </c>
-      <c r="C84" t="s">
-        <v>539</v>
-      </c>
-      <c r="D84" t="s">
-        <v>159</v>
-      </c>
-      <c r="E84" t="s">
-        <v>540</v>
-      </c>
-      <c r="F84" t="s">
-        <v>154</v>
-      </c>
-      <c r="H84" s="2" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B85" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C85" t="s">
+        <v>158</v>
+      </c>
+      <c r="D85" t="s">
+        <v>159</v>
+      </c>
+      <c r="E85" t="s">
+        <v>167</v>
+      </c>
+      <c r="F85" t="s">
+        <v>541</v>
+      </c>
+      <c r="H85" s="2" t="s">
         <v>542</v>
-      </c>
-      <c r="D85" t="s">
-        <v>159</v>
-      </c>
-      <c r="E85" t="s">
-        <v>540</v>
-      </c>
-      <c r="F85" t="s">
-        <v>154</v>
-      </c>
-      <c r="H85" s="2" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="B86" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="C86" t="s">
-        <v>368</v>
+        <v>158</v>
       </c>
       <c r="D86" t="s">
         <v>159</v>
       </c>
       <c r="E86" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="F86" t="s">
-        <v>154</v>
+        <v>546</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>537</v>
+        <v>548</v>
       </c>
       <c r="B87" t="s">
-        <v>538</v>
+        <v>549</v>
       </c>
       <c r="C87" t="s">
-        <v>188</v>
+        <v>158</v>
       </c>
       <c r="D87" t="s">
         <v>159</v>
       </c>
       <c r="E87" t="s">
-        <v>540</v>
+        <v>550</v>
       </c>
       <c r="F87" t="s">
-        <v>154</v>
+        <v>551</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>545</v>
+        <v>552</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>546</v>
+        <v>553</v>
       </c>
       <c r="B88" t="s">
-        <v>547</v>
+        <v>236</v>
       </c>
       <c r="C88" t="s">
-        <v>548</v>
+        <v>237</v>
       </c>
       <c r="D88" t="s">
         <v>159</v>
       </c>
       <c r="E88" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="F88" t="s">
-        <v>550</v>
+        <v>178</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="B89" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="C89" t="s">
+        <v>558</v>
+      </c>
+      <c r="D89" t="s">
+        <v>159</v>
+      </c>
+      <c r="E89" t="s">
+        <v>559</v>
+      </c>
+      <c r="F89" t="s">
+        <v>560</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>562</v>
+      </c>
+      <c r="B90" t="s">
+        <v>563</v>
+      </c>
+      <c r="C90" t="s">
+        <v>209</v>
+      </c>
+      <c r="D90" t="s">
+        <v>340</v>
+      </c>
+      <c r="E90" t="s">
+        <v>564</v>
+      </c>
+      <c r="F90" t="s">
+        <v>296</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>566</v>
+      </c>
+      <c r="B91" t="s">
+        <v>567</v>
+      </c>
+      <c r="C91" t="s">
+        <v>568</v>
+      </c>
+      <c r="D91" t="s">
+        <v>152</v>
+      </c>
+      <c r="E91" t="s">
+        <v>167</v>
+      </c>
+      <c r="F91" t="s">
+        <v>569</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>571</v>
+      </c>
+      <c r="B92" t="s">
+        <v>572</v>
+      </c>
+      <c r="C92" t="s">
+        <v>573</v>
+      </c>
+      <c r="D92" t="s">
+        <v>159</v>
+      </c>
+      <c r="E92" t="s">
+        <v>574</v>
+      </c>
+      <c r="F92" t="s">
+        <v>575</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>577</v>
+      </c>
+      <c r="B93" t="s">
+        <v>572</v>
+      </c>
+      <c r="C93" t="s">
+        <v>578</v>
+      </c>
+      <c r="D93" t="s">
+        <v>159</v>
+      </c>
+      <c r="E93" t="s">
+        <v>574</v>
+      </c>
+      <c r="F93" t="s">
+        <v>575</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>580</v>
+      </c>
+      <c r="B94" t="s">
+        <v>581</v>
+      </c>
+      <c r="C94" t="s">
+        <v>421</v>
+      </c>
+      <c r="D94" t="s">
+        <v>159</v>
+      </c>
+      <c r="E94" t="s">
+        <v>582</v>
+      </c>
+      <c r="F94" t="s">
+        <v>583</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>585</v>
+      </c>
+      <c r="B95" t="s">
+        <v>586</v>
+      </c>
+      <c r="C95" t="s">
+        <v>421</v>
+      </c>
+      <c r="D95" t="s">
+        <v>159</v>
+      </c>
+      <c r="E95" t="s">
+        <v>587</v>
+      </c>
+      <c r="F95" t="s">
+        <v>588</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>590</v>
+      </c>
+      <c r="B96" t="s">
+        <v>591</v>
+      </c>
+      <c r="C96" t="s">
+        <v>592</v>
+      </c>
+      <c r="D96" t="s">
+        <v>159</v>
+      </c>
+      <c r="E96" t="s">
+        <v>593</v>
+      </c>
+      <c r="F96" t="s">
+        <v>594</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>596</v>
+      </c>
+      <c r="B97" t="s">
+        <v>591</v>
+      </c>
+      <c r="C97" t="s">
+        <v>597</v>
+      </c>
+      <c r="D97" t="s">
+        <v>159</v>
+      </c>
+      <c r="E97" t="s">
+        <v>593</v>
+      </c>
+      <c r="F97" t="s">
+        <v>594</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>599</v>
+      </c>
+      <c r="B98" t="s">
+        <v>586</v>
+      </c>
+      <c r="C98" t="s">
+        <v>209</v>
+      </c>
+      <c r="D98" t="s">
+        <v>159</v>
+      </c>
+      <c r="E98" t="s">
+        <v>600</v>
+      </c>
+      <c r="F98" t="s">
+        <v>588</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>602</v>
+      </c>
+      <c r="B99" t="s">
+        <v>603</v>
+      </c>
+      <c r="C99" t="s">
+        <v>326</v>
+      </c>
+      <c r="D99" t="s">
+        <v>159</v>
+      </c>
+      <c r="E99" t="s">
+        <v>604</v>
+      </c>
+      <c r="F99" t="s">
+        <v>167</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>606</v>
+      </c>
+      <c r="B100" t="s">
+        <v>607</v>
+      </c>
+      <c r="C100" t="s">
+        <v>300</v>
+      </c>
+      <c r="D100" t="s">
+        <v>159</v>
+      </c>
+      <c r="E100" t="s">
+        <v>432</v>
+      </c>
+      <c r="F100" t="s">
+        <v>608</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>610</v>
+      </c>
+      <c r="B101" t="s">
+        <v>611</v>
+      </c>
+      <c r="C101" t="s">
+        <v>300</v>
+      </c>
+      <c r="D101" t="s">
+        <v>159</v>
+      </c>
+      <c r="E101" t="s">
+        <v>612</v>
+      </c>
+      <c r="F101" t="s">
+        <v>613</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>615</v>
+      </c>
+      <c r="B102" t="s">
+        <v>616</v>
+      </c>
+      <c r="C102" t="s">
+        <v>300</v>
+      </c>
+      <c r="D102" t="s">
+        <v>152</v>
+      </c>
+      <c r="E102" t="s">
+        <v>617</v>
+      </c>
+      <c r="F102" t="s">
         <v>271</v>
       </c>
-      <c r="D89" t="s">
-        <v>159</v>
-      </c>
-      <c r="E89" t="s">
-        <v>554</v>
-      </c>
-      <c r="F89" t="s">
-        <v>412</v>
-      </c>
-      <c r="H89" s="2" t="s">
-        <v>555</v>
+      <c r="H102" s="2" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>619</v>
+      </c>
+      <c r="B103" t="s">
+        <v>620</v>
+      </c>
+      <c r="C103" t="s">
+        <v>421</v>
+      </c>
+      <c r="D103" t="s">
+        <v>159</v>
+      </c>
+      <c r="E103" t="s">
+        <v>167</v>
+      </c>
+      <c r="F103" t="s">
+        <v>167</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>622</v>
+      </c>
+      <c r="B104" t="s">
+        <v>623</v>
+      </c>
+      <c r="C104" t="s">
+        <v>300</v>
+      </c>
+      <c r="D104" t="s">
+        <v>159</v>
+      </c>
+      <c r="E104" t="s">
+        <v>624</v>
+      </c>
+      <c r="F104" t="s">
+        <v>625</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>627</v>
+      </c>
+      <c r="B105" t="s">
+        <v>628</v>
+      </c>
+      <c r="C105" t="s">
+        <v>436</v>
+      </c>
+      <c r="D105" t="s">
+        <v>159</v>
+      </c>
+      <c r="E105" t="s">
+        <v>550</v>
+      </c>
+      <c r="F105" t="s">
+        <v>629</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>631</v>
+      </c>
+      <c r="B106" t="s">
+        <v>632</v>
+      </c>
+      <c r="C106" t="s">
+        <v>633</v>
+      </c>
+      <c r="D106" t="s">
+        <v>159</v>
+      </c>
+      <c r="E106" t="s">
+        <v>634</v>
+      </c>
+      <c r="F106" t="s">
+        <v>635</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>637</v>
+      </c>
+      <c r="B107" t="s">
+        <v>638</v>
+      </c>
+      <c r="C107" t="s">
+        <v>300</v>
+      </c>
+      <c r="D107" t="s">
+        <v>159</v>
+      </c>
+      <c r="E107" t="s">
+        <v>639</v>
+      </c>
+      <c r="F107" t="s">
+        <v>167</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>637</v>
+      </c>
+      <c r="B108" t="s">
+        <v>638</v>
+      </c>
+      <c r="C108" t="s">
+        <v>641</v>
+      </c>
+      <c r="D108" t="s">
+        <v>159</v>
+      </c>
+      <c r="E108" t="s">
+        <v>639</v>
+      </c>
+      <c r="F108" t="s">
+        <v>167</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>637</v>
+      </c>
+      <c r="B109" t="s">
+        <v>638</v>
+      </c>
+      <c r="C109" t="s">
+        <v>300</v>
+      </c>
+      <c r="D109" t="s">
+        <v>159</v>
+      </c>
+      <c r="E109" t="s">
+        <v>639</v>
+      </c>
+      <c r="F109" t="s">
+        <v>167</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>644</v>
+      </c>
+      <c r="B110" t="s">
+        <v>279</v>
+      </c>
+      <c r="C110" t="s">
+        <v>242</v>
+      </c>
+      <c r="D110" t="s">
+        <v>159</v>
+      </c>
+      <c r="E110" t="s">
+        <v>645</v>
+      </c>
+      <c r="F110" t="s">
+        <v>281</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>647</v>
+      </c>
+      <c r="B111" t="s">
+        <v>648</v>
+      </c>
+      <c r="C111" t="s">
+        <v>209</v>
+      </c>
+      <c r="D111" t="s">
+        <v>159</v>
+      </c>
+      <c r="E111" t="s">
+        <v>649</v>
+      </c>
+      <c r="F111" t="s">
+        <v>650</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>652</v>
+      </c>
+      <c r="B112" t="s">
+        <v>648</v>
+      </c>
+      <c r="C112" t="s">
+        <v>209</v>
+      </c>
+      <c r="D112" t="s">
+        <v>159</v>
+      </c>
+      <c r="E112" t="s">
+        <v>653</v>
+      </c>
+      <c r="F112" t="s">
+        <v>650</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>655</v>
+      </c>
+      <c r="B113" t="s">
+        <v>656</v>
+      </c>
+      <c r="C113" t="s">
+        <v>657</v>
+      </c>
+      <c r="D113" t="s">
+        <v>159</v>
+      </c>
+      <c r="E113" t="s">
+        <v>167</v>
+      </c>
+      <c r="F113" t="s">
+        <v>658</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>660</v>
+      </c>
+      <c r="B114" t="s">
+        <v>661</v>
+      </c>
+      <c r="C114" t="s">
+        <v>662</v>
+      </c>
+      <c r="D114" t="s">
+        <v>159</v>
+      </c>
+      <c r="E114" t="s">
+        <v>663</v>
+      </c>
+      <c r="F114" t="s">
+        <v>154</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>660</v>
+      </c>
+      <c r="B115" t="s">
+        <v>661</v>
+      </c>
+      <c r="C115" t="s">
+        <v>665</v>
+      </c>
+      <c r="D115" t="s">
+        <v>159</v>
+      </c>
+      <c r="E115" t="s">
+        <v>663</v>
+      </c>
+      <c r="F115" t="s">
+        <v>154</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>660</v>
+      </c>
+      <c r="B116" t="s">
+        <v>661</v>
+      </c>
+      <c r="C116" t="s">
+        <v>183</v>
+      </c>
+      <c r="D116" t="s">
+        <v>159</v>
+      </c>
+      <c r="E116" t="s">
+        <v>663</v>
+      </c>
+      <c r="F116" t="s">
+        <v>154</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>660</v>
+      </c>
+      <c r="B117" t="s">
+        <v>661</v>
+      </c>
+      <c r="C117" t="s">
+        <v>209</v>
+      </c>
+      <c r="D117" t="s">
+        <v>159</v>
+      </c>
+      <c r="E117" t="s">
+        <v>663</v>
+      </c>
+      <c r="F117" t="s">
+        <v>154</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>669</v>
+      </c>
+      <c r="B118" t="s">
+        <v>670</v>
+      </c>
+      <c r="C118" t="s">
+        <v>421</v>
+      </c>
+      <c r="D118" t="s">
+        <v>159</v>
+      </c>
+      <c r="E118" t="s">
+        <v>671</v>
+      </c>
+      <c r="F118" t="s">
+        <v>154</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>673</v>
+      </c>
+      <c r="B119" t="s">
+        <v>674</v>
+      </c>
+      <c r="C119" t="s">
+        <v>675</v>
+      </c>
+      <c r="D119" t="s">
+        <v>159</v>
+      </c>
+      <c r="E119" t="s">
+        <v>676</v>
+      </c>
+      <c r="F119" t="s">
+        <v>677</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>679</v>
+      </c>
+      <c r="B120" t="s">
+        <v>680</v>
+      </c>
+      <c r="C120" t="s">
+        <v>311</v>
+      </c>
+      <c r="D120" t="s">
+        <v>159</v>
+      </c>
+      <c r="E120" t="s">
+        <v>681</v>
+      </c>
+      <c r="F120" t="s">
+        <v>506</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>682</v>
       </c>
     </row>
   </sheetData>
@@ -4919,6 +6013,37 @@
     <hyperlink ref="H87" r:id="rId86"/>
     <hyperlink ref="H88" r:id="rId87"/>
     <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
+    <hyperlink ref="H105" r:id="rId104"/>
+    <hyperlink ref="H106" r:id="rId105"/>
+    <hyperlink ref="H107" r:id="rId106"/>
+    <hyperlink ref="H108" r:id="rId107"/>
+    <hyperlink ref="H109" r:id="rId108"/>
+    <hyperlink ref="H110" r:id="rId109"/>
+    <hyperlink ref="H111" r:id="rId110"/>
+    <hyperlink ref="H112" r:id="rId111"/>
+    <hyperlink ref="H113" r:id="rId112"/>
+    <hyperlink ref="H114" r:id="rId113"/>
+    <hyperlink ref="H115" r:id="rId114"/>
+    <hyperlink ref="H116" r:id="rId115"/>
+    <hyperlink ref="H117" r:id="rId116"/>
+    <hyperlink ref="H118" r:id="rId117"/>
+    <hyperlink ref="H119" r:id="rId118"/>
+    <hyperlink ref="H120" r:id="rId119"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
